--- a/Assets/_ProtoType_Merge/ASB/Data/Excel/이벤트 스크립트 테이블_1구역_ver1.3.xlsx
+++ b/Assets/_ProtoType_Merge/ASB/Data/Excel/이벤트 스크립트 테이블_1구역_ver1.3.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\카카오톡 받은 파일\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\k2104200013\Desktop\프로젝트HI\2_Documents\이기석\채팅 시스템\1구역\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E0C7F66-C9B0-4EE7-A5BA-E60DE0A1E776}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9DDB0F-9982-4488-8640-66CDEF72220B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17460" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -540,7 +540,7 @@
   <si>
     <t>거점 탈환 직후 실행 이벤트
 당신은 성공적으로 거점을 탈환하고, 다음 목적지를 정한다.
-이때 빌런연합의 수장 마돈나가 연락해 당신을 도발한다.
+이때 빌런연합의 수장 율리아가 연락해 당신을 도발한다.
 도발에 응한 당신은 다음 탈환지를 찾아 다른 구역으로 이동한다.</t>
   </si>
   <si>
@@ -1093,9 +1093,6 @@
     <t>루미나의 지원포격 덕에 인질을 걱정할 필요가 없어졌다.</t>
   </si>
   <si>
-    <t>우선 인질부터 구출하자.</t>
-  </si>
-  <si>
     <t>그 엔지니어가 한 말이 사실이라면, 비밀 통로를 통해 인질을 구출할 수 있을 거야.</t>
   </si>
   <si>
@@ -1483,13 +1480,7 @@
     <t>Flag_RuminaExplosionDeny!=1</t>
   </si>
   <si>
-    <t>루미나가 밖에서 사주경계하는 동안 조용히 뒷문으로 잠입하자.</t>
-  </si>
-  <si>
     <t>3A</t>
-  </si>
-  <si>
-    <t>블랙불릿과 저스티스가 먼저 인질부터 구출해.</t>
   </si>
   <si>
     <t>Set_Flag_1CectorHiddenRoute</t>
@@ -1522,542 +1513,558 @@
 Stat</t>
   </si>
   <si>
+    <t>HostageInjuredCount &gt;= 3</t>
+  </si>
+  <si>
+    <t>Reward_0010\Set_Flag_1SectorMainEventClear</t>
+  </si>
+  <si>
+    <t>인질 3명 부상</t>
+  </si>
+  <si>
+    <t>Reward_0020\Set_Flag_1SectorMainEventClear</t>
+  </si>
+  <si>
+    <t>인질 1~2명 부상</t>
+  </si>
+  <si>
+    <t>HostageInjuredCount = 10</t>
+  </si>
+  <si>
+    <t>Set_Flag_1SectorMainEventClear</t>
+  </si>
+  <si>
+    <t>인질 모두 구출</t>
+  </si>
+  <si>
+    <t>Set_Flag_1CectorHiddenRoute==1</t>
+  </si>
+  <si>
+    <t>소녀가 무너진 골목 입구에서 울먹이며 히어로들을 붙잡는다.</t>
+  </si>
+  <si>
+    <t>겁먹은 소녀</t>
+  </si>
+  <si>
+    <t>히어로님… 혹시 제 오빠 못 보셨어요?</t>
+  </si>
+  <si>
+    <t>오빠?</t>
+  </si>
+  <si>
+    <t>어제부터 집에 안 들어왔어요. 엄마는 오빠가 또 사고쳤다고만 하는데…</t>
+  </si>
+  <si>
+    <t>오빠가 나쁜 애는 맞지만, 그래도 빌런한테 잡혀가면 안 되잖아요.</t>
+  </si>
+  <si>
+    <t>나쁜 애는 맞다고 못박는구나. 가족 평가가 신랄한데?</t>
+  </si>
+  <si>
+    <t>어떻게 할까?</t>
+  </si>
+  <si>
+    <t>도와줄게. 마지막으로 본 곳부터 알려줘.</t>
+  </si>
+  <si>
+    <t>정말요? 공구상 뒤편 골목에서 수상한 사람들과 얘기하는 걸 봤어요.</t>
+  </si>
+  <si>
+    <t>공구상… 빌런 연합 선발대가 점거했다던 곳 근처네요.</t>
+  </si>
+  <si>
+    <t>도와주긴 할 건데, 위험한 일이면 사례가 필요해.</t>
+  </si>
+  <si>
+    <t>제… 제 저금통 드릴게요. 동전이랑, 반짝이는 병뚜껑도 있어요.</t>
+  </si>
+  <si>
+    <t>관리자. 방금 어린애 상대로 협상한 거야?</t>
+  </si>
+  <si>
+    <t>정보의 대가를 명확히 한 거야. 법적으로는… 아마…</t>
+  </si>
+  <si>
+    <t>소녀는 오빠가 남기고 간 찢어진 작업 장갑을 건넸다.</t>
+  </si>
+  <si>
+    <t>좋다! 실종된 시민을 구하는 일 또한 정의의 길이다!</t>
+  </si>
+  <si>
+    <t>오빠가 사라진 골목의 흔적을 추적할 수 있게 되었다.</t>
+  </si>
+  <si>
+    <t>공구상 뒤편 골목에는 버려진 공구 상자와 급히 지운 발자국이 남아 있었다.</t>
+  </si>
+  <si>
+    <t>흠, 이거 봐. 작업 장갑이랑 같은 기름 냄새.</t>
+  </si>
+  <si>
+    <t>발자국은 안쪽 창고로 이어져요. 그런데… 누가 끌려간 흔적은 아니에요.</t>
+  </si>
+  <si>
+    <t>스스로 걸어갔다고?</t>
+  </si>
+  <si>
+    <t>불량한 청년</t>
+  </si>
+  <si>
+    <t>아, 진짜. 난 히어로 같은 거 부른 적 없는데?</t>
+  </si>
+  <si>
+    <t>찾았다! 납치 피해자!</t>
+  </si>
+  <si>
+    <t>피해자 아니거든? 나 이제 빌런 연합 소속이거든?</t>
+  </si>
+  <si>
+    <t>와, 인생 선택지가 저렇게 노골적으로 틀릴 수 있구나.</t>
+  </si>
+  <si>
+    <t>오빠는 빌런 연합에 들어가 한몫 챙기려 했다고 털어놓았다.</t>
+  </si>
+  <si>
+    <t>동생이 널 찾고 있어. 지금이라도 돌아가.</t>
+  </si>
+  <si>
+    <t>웃기지 마. 돌아가면 또 잔소리뿐이야.</t>
+  </si>
+  <si>
+    <t>잔소리할 사람이 있다는 건… 돌아갈 곳이 있다는 뜻 아닐까요?</t>
+  </si>
+  <si>
+    <t>…그런 말로 흔들리지 않거든.</t>
+  </si>
+  <si>
+    <t>주변 빌런부터 제압하고 이야기하자.</t>
+  </si>
+  <si>
+    <t>동네 빌런</t>
+  </si>
+  <si>
+    <t>어이 신입! 저 히어로들 네가 부른 거냐?</t>
+  </si>
+  <si>
+    <t>아, 아니거든요! 저 아직 배신 안 했거든요!</t>
+  </si>
+  <si>
+    <t>약속한 사례를 생각하면, 네가 왜 여기 왔는지 정확히 들어야겠어.</t>
+  </si>
+  <si>
+    <t>사례? 그 꼬맹이가 뭘 준다고 했는데?</t>
+  </si>
+  <si>
+    <t>반짝이는 병뚜껑. 시장 가치가 폭락하기 전에 협조해.</t>
+  </si>
+  <si>
+    <t>그 순간 창고 안쪽에서 빌런들의 고함이 들려왔다.</t>
+  </si>
+  <si>
+    <t>신입은 여기까지다! 공구상 위치를 알았으면 입막음해야지!</t>
+  </si>
+  <si>
+    <t>뭐? 잠깐, 나 아직 정식 계약서도 못 썼는데?</t>
+  </si>
+  <si>
+    <t>오빠는 빌런 연합에게도 버림받은 처지였다.</t>
+  </si>
+  <si>
+    <t>빌런들은 오빠를 묶어 공구상 보강 작업장으로 끌고 갔다.</t>
+  </si>
+  <si>
+    <t>오빠! 오빠 맞죠?!</t>
+  </si>
+  <si>
+    <t>야! 왜 여기까지 왔어! 집에 가라니까!</t>
+  </si>
+  <si>
+    <t>비록 길을 잘못 들었으나, 가족을 걱정하는 마음만은 진짜다!</t>
+  </si>
+  <si>
+    <t>그럼 묶은 줄만 태우면 되지?</t>
+  </si>
+  <si>
+    <t>줄만 태울 수 있어?</t>
+  </si>
+  <si>
+    <t>그런 세세한 주문은 안 받아.</t>
+  </si>
+  <si>
+    <t>그럼 안 돼요! 주변에 기름통이 있어요!</t>
+  </si>
+  <si>
+    <t>구출 방식을 정하자.</t>
+  </si>
+  <si>
+    <t>정면에서 시선을 끌자. 블랙불릿은 오빠를 빼내.</t>
+  </si>
+  <si>
+    <t>좋아. 난 위험한 역할이 제일 싫으니까 빨리 끝낼게.</t>
+  </si>
+  <si>
+    <t>히어로다! 장비부터 챙겨!</t>
+  </si>
+  <si>
+    <t>정면 돌파로 소동이 커졌지만, 오빠를 구출할 틈은 생겼다.</t>
+  </si>
+  <si>
+    <t>빌런들이 버린 작업 동선을 역으로 이용하자.</t>
+  </si>
+  <si>
+    <t>잠깐, 그 길은 공구상 안쪽으로 바로 이어져. 인질들이 있는 쪽이야.</t>
+  </si>
+  <si>
+    <t>그럼 이 정보가 있으면 공구상 인질을 먼저 구할 수 있겠네요!</t>
+  </si>
+  <si>
+    <t>훌륭하다! 잘못을 뉘우치는 마음은 정의로 돌아오는 첫걸음이다!</t>
+  </si>
+  <si>
+    <t>오빠는 소녀에게 잔뜩 혼난 뒤, 공구상 안쪽으로 이어지는 숨은 작업 통로를 알려주었다.</t>
+  </si>
+  <si>
+    <t>나 같은 거 구해줘서… 미안하다. 그리고 고마워.</t>
+  </si>
+  <si>
+    <t>집 가면 엄마한테도 똑같이 말해.</t>
+  </si>
+  <si>
+    <t>소녀와 오빠는 무사히 귀가했고, 오빠는 공구상 안쪽 작업 통로 정보를 넘겨주었다.</t>
+  </si>
+  <si>
+    <t>협회 임시 게시판에 이상한 제보가 붙었다.</t>
+  </si>
+  <si>
+    <t>편의점 점주</t>
+  </si>
+  <si>
+    <t>히어로님들! 우리 가게 진상만 골라 털어가는 빌런이 나타났습니다!</t>
+  </si>
+  <si>
+    <t>진상만?</t>
+  </si>
+  <si>
+    <t>예. 라면 국물 엎고 도망친 손님, 동전 던진 손님, 전부 다음날 지갑이 털렸어요.</t>
+  </si>
+  <si>
+    <t>좋은 사람 아니야?</t>
+  </si>
+  <si>
+    <t>아니다! 사적 제재는 정의가 아니다!</t>
+  </si>
+  <si>
+    <t>조사 방향을 정하자.</t>
+  </si>
+  <si>
+    <t>피해자 영수증과 CCTV 시간부터 대조하자.</t>
+  </si>
+  <si>
+    <t>피해자들이 모두 같은 시간대에 같은 물건을 샀어요. 컵라면, 삼각김밥, 그리고… 진상짓.</t>
+  </si>
+  <si>
+    <t>마지막 품목은 바코드가 없을 텐데.</t>
+  </si>
+  <si>
+    <t>오늘 밤 편의점 앞에서 잠복하자.</t>
+  </si>
+  <si>
+    <t>좋아. 진상이 오면 내가 먼저 화를 내도 돼?</t>
+  </si>
+  <si>
+    <t>그럼 잠복이 아니라 사건 현장 재현이야.</t>
+  </si>
+  <si>
+    <t>빌런이면 일단 잡고 보자.</t>
+  </si>
+  <si>
+    <t>그 기백은 훌륭하나, 범인을 모르면 잡을 수도 없다!</t>
+  </si>
+  <si>
+    <t>조사 끝에 범인이 편의점 진상들의 동선을 미리 알고 움직인다는 사실을 알아냈다.</t>
+  </si>
+  <si>
+    <t>히어로들은 편의점 빌런이 남긴 검은 명단을 따라 오로라 골목을 추적했다.</t>
+  </si>
+  <si>
+    <t>명단에 피해자 이름 옆으로 별점이 있어요.</t>
+  </si>
+  <si>
+    <t>진상 등급표네. 별 다섯 개는 뭘 해야 받는 거야?</t>
+  </si>
+  <si>
+    <t>전자레인지에 생달걀을 넣고 터뜨린 손님입니다.</t>
+  </si>
+  <si>
+    <t>그건 빌런 맞지 않아?</t>
+  </si>
+  <si>
+    <t>그래도 우리가 잡아야 할 건 편의점 빌런이야.</t>
+  </si>
+  <si>
+    <t>명단 뒤에는 빌런 연합의 물자 이동 시간표가 작게 적혀 있었다.</t>
+  </si>
+  <si>
+    <t>이 사람, 진상만 쫓은 게 아니라 빌런 물자까지 훔치고 있었어요.</t>
+  </si>
+  <si>
+    <t>추적 방법을 정하자.</t>
+  </si>
+  <si>
+    <t>명단의 다음 표적을 보호하며 기다리자.</t>
+  </si>
+  <si>
+    <t>보호 대상이 별 다섯 개 진상인 건 조금 고통스럽네.</t>
+  </si>
+  <si>
+    <t>편의점 직원들에게 범인의 습관을 묻자.</t>
+  </si>
+  <si>
+    <t>전직 알바생</t>
+  </si>
+  <si>
+    <t>범인은 꼭 계산대 앞에서 '어서오세요'를 혼잣말로 해요. 버릇처럼요.</t>
+  </si>
+  <si>
+    <t>그 말엔 슬픔이 묻어 있군.</t>
+  </si>
+  <si>
+    <t>추적 끝에 편의점 빌런이 버려진 무인 편의점에 숨어 있다는 사실을 알아냈다.</t>
+  </si>
+  <si>
+    <t>버려진 무인 편의점 안에는 빼곡한 진상 명단과 빌런 연합 물자 상자가 쌓여 있었다.</t>
+  </si>
+  <si>
+    <t>편의점 빌런</t>
+  </si>
+  <si>
+    <t>어서오세요. 아니, 오지 마세요. 당신들은 어떤 진상입니까?</t>
+  </si>
+  <si>
+    <t>우린 히어로다.</t>
+  </si>
+  <si>
+    <t>히어로? 제가 되고 싶었던 바로 그 직업이군요.</t>
+  </si>
+  <si>
+    <t>하지만 협회는 제 이상을 거절했습니다. 모든 진상을 구축하겠다는 숭고한 꿈을요.</t>
+  </si>
+  <si>
+    <t>협회가 의외로 정상적인 판단을 했네.</t>
+  </si>
+  <si>
+    <t>그래서 제가 직접 세상을 정화하기로 했습니다. 시민도, 빌런도, 진상이라면 예외 없습니다.</t>
+  </si>
+  <si>
+    <t>그건 정의가 아니다. 분노에 이름표를 붙였을 뿐이다!</t>
+  </si>
+  <si>
+    <t>대응을 정하자.</t>
+  </si>
+  <si>
+    <t>당장 제압한다. 더 피해가 나기 전에 끝내자.</t>
+  </si>
+  <si>
+    <t>진상을 감싸는 자도 진상입니다!</t>
+  </si>
+  <si>
+    <t>편의점 빌런은 계산대 바코드 스캐너를 검처럼 들고 달려들었다.</t>
+  </si>
+  <si>
+    <t>네가 겪은 일은 알겠어. 하지만 그걸로 남을 해칠 권리는 없어.</t>
+  </si>
+  <si>
+    <t>권리요? 진상들은 제게 그런 걸 묻지 않았습니다.</t>
+  </si>
+  <si>
+    <t>그래도 누군가를 다치게 하면, 당신도 똑같이 누군가의 공포가 돼요.</t>
+  </si>
+  <si>
+    <t>…그 말, 교대 근무 끝나고 들었으면 조금 위로가 됐겠네요.</t>
+  </si>
+  <si>
+    <t>저스티스, 전직 히어로 지망생으로서 면접을 다시 봐줘.</t>
+  </si>
+  <si>
+    <t>좋다! 첫 질문이다. 진상이란 무엇인가!</t>
+  </si>
+  <si>
+    <t>그 면접, 오늘 안에 끝나긴 해?</t>
+  </si>
+  <si>
+    <t>격전 끝에 편의점 빌런은 제압되었고, 그가 모은 빌런 연합 은닉 자원 위치 정보가 확보되었다.</t>
+  </si>
+  <si>
+    <t>그 자료는… 진상을 막기 위해 모은 겁니다. 부디 제대로 써주세요.</t>
+  </si>
+  <si>
+    <t>그래. 적어도 네가 못 이룬 좋은 일에는 쓰이게 할게.</t>
+  </si>
+  <si>
+    <t>오로라 1구역의 숨겨진 자원 구역 일부가 지도에 표시되었다.</t>
+  </si>
+  <si>
+    <t>Set_Flag_SubEvent1Accept</t>
+  </si>
+  <si>
+    <t>서브 이벤트1_1 수락</t>
+  </si>
+  <si>
+    <t>Set_Flag_SubEvent1RewardDemand</t>
+  </si>
+  <si>
+    <t>보상 요구 루트</t>
+  </si>
+  <si>
+    <t>Set_Flag_SubEvent1Start</t>
+  </si>
+  <si>
+    <t>오빠 추적 시작</t>
+  </si>
+  <si>
+    <t>Set_Flag_BrotherPersuade</t>
+  </si>
+  <si>
+    <t>설득 루트</t>
+  </si>
+  <si>
+    <t>Start_Battle_1050</t>
+  </si>
+  <si>
+    <t>골목 빌런전</t>
+  </si>
+  <si>
+    <t>Flag_SubEvent1RewardDemand==1</t>
+  </si>
+  <si>
+    <t>약속한 사례부터 확인한다.</t>
+  </si>
+  <si>
+    <t>보상 요구 선택 시 노출</t>
+  </si>
+  <si>
+    <t>Set_Flag_SubEvent1Truth</t>
+  </si>
+  <si>
+    <t>오빠의 진실 확인</t>
+  </si>
+  <si>
+    <t>Start_Battle_1060</t>
+  </si>
+  <si>
+    <t>정면 구출</t>
+  </si>
+  <si>
+    <t>Flag_SubEvent1Truth==1</t>
+  </si>
+  <si>
+    <t>서브 이벤트1 내부 단서 활용</t>
+  </si>
+  <si>
+    <t>Flag_1SectorMainEventClear==1</t>
+  </si>
+  <si>
+    <t>메인 이벤트 클리어 후 완료 보상 대체</t>
+  </si>
+  <si>
+    <t>서브 이벤트1 완료: 공구상 인질 구출 히든 루트 해금</t>
+  </si>
+  <si>
+    <t>단서 조사</t>
+  </si>
+  <si>
+    <t>잠복 조사</t>
+  </si>
+  <si>
+    <t>무작정 수색</t>
+  </si>
+  <si>
+    <t>Set_Flag_SubEvent2Start</t>
+  </si>
+  <si>
+    <t>편의점 빌런 추적 시작</t>
+  </si>
+  <si>
+    <t>표적 보호</t>
+  </si>
+  <si>
+    <t>직원 탐문</t>
+  </si>
+  <si>
+    <t>Set_Flag_SubEvent2TraceComplete</t>
+  </si>
+  <si>
+    <t>은신처 발견</t>
+  </si>
+  <si>
+    <t>Start_Battle_1080</t>
+  </si>
+  <si>
+    <t>편의점 빌런전</t>
+  </si>
+  <si>
+    <t>설득 시도</t>
+  </si>
+  <si>
+    <t>Stat</t>
+  </si>
+  <si>
+    <t>Justice_IP &gt;= 30</t>
+  </si>
+  <si>
+    <t>저스티스 I.P 조건</t>
+  </si>
+  <si>
+    <t>서브 이벤트2 완료</t>
+  </si>
+  <si>
+    <t>Set_Flag_SubEvent1Complete\
+Reward_AllHeroIP_001</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set_Flag_SubEvent1Complete\
+Set_Flag_1CectorHiddenRoute\
+Reward_1SectorHiddenRoute</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set_Flag_SubEvent2Complete\
+Reward_AllHeroIP_002</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>Set_Flag_SubEvent2Complete\
+Reveal_Fog_Level2\
+Reward_1SectorHiddenResource</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>집 나간 오빠의 진상 파악</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
     <t>Rumina_IP =&lt; 20\
 Justice_IP =&lt; 20\
 BlackBullet_IP =&lt; 20\
 Nekoming_IP =&lt; 20</t>
-  </si>
-  <si>
-    <t>HostageInjuredCount &gt;= 3</t>
-  </si>
-  <si>
-    <t>Reward_0010\Set_Flag_1SectorMainEventClear</t>
-  </si>
-  <si>
-    <t>인질 3명 부상</t>
-  </si>
-  <si>
-    <t>2 &gt;= HostageInjuredCount &gt;= 1</t>
-  </si>
-  <si>
-    <t>Reward_0020\Set_Flag_1SectorMainEventClear</t>
-  </si>
-  <si>
-    <t>인질 1~2명 부상</t>
-  </si>
-  <si>
-    <t>HostageInjuredCount = 10</t>
-  </si>
-  <si>
-    <t>Set_Flag_1SectorMainEventClear</t>
-  </si>
-  <si>
-    <t>인질 모두 구출</t>
-  </si>
-  <si>
-    <t>Set_Flag_1CectorHiddenRoute==1</t>
-  </si>
-  <si>
-    <t>소녀가 무너진 골목 입구에서 울먹이며 히어로들을 붙잡는다.</t>
-  </si>
-  <si>
-    <t>겁먹은 소녀</t>
-  </si>
-  <si>
-    <t>히어로님… 혹시 제 오빠 못 보셨어요?</t>
-  </si>
-  <si>
-    <t>오빠?</t>
-  </si>
-  <si>
-    <t>어제부터 집에 안 들어왔어요. 엄마는 오빠가 또 사고쳤다고만 하는데…</t>
-  </si>
-  <si>
-    <t>오빠가 나쁜 애는 맞지만, 그래도 빌런한테 잡혀가면 안 되잖아요.</t>
-  </si>
-  <si>
-    <t>나쁜 애는 맞다고 못박는구나. 가족 평가가 신랄한데?</t>
-  </si>
-  <si>
-    <t>어떻게 할까?</t>
-  </si>
-  <si>
-    <t>도와줄게. 마지막으로 본 곳부터 알려줘.</t>
-  </si>
-  <si>
-    <t>정말요? 공구상 뒤편 골목에서 수상한 사람들과 얘기하는 걸 봤어요.</t>
-  </si>
-  <si>
-    <t>공구상… 빌런 연합 선발대가 점거했다던 곳 근처네요.</t>
-  </si>
-  <si>
-    <t>도와주긴 할 건데, 위험한 일이면 사례가 필요해.</t>
-  </si>
-  <si>
-    <t>제… 제 저금통 드릴게요. 동전이랑, 반짝이는 병뚜껑도 있어요.</t>
-  </si>
-  <si>
-    <t>관리자. 방금 어린애 상대로 협상한 거야?</t>
-  </si>
-  <si>
-    <t>정보의 대가를 명확히 한 거야. 법적으로는… 아마…</t>
-  </si>
-  <si>
-    <t>소녀는 오빠가 남기고 간 찢어진 작업 장갑을 건넸다.</t>
-  </si>
-  <si>
-    <t>좋다! 실종된 시민을 구하는 일 또한 정의의 길이다!</t>
-  </si>
-  <si>
-    <t>오빠가 사라진 골목의 흔적을 추적할 수 있게 되었다.</t>
-  </si>
-  <si>
-    <t>공구상 뒤편 골목에는 버려진 공구 상자와 급히 지운 발자국이 남아 있었다.</t>
-  </si>
-  <si>
-    <t>흠, 이거 봐. 작업 장갑이랑 같은 기름 냄새.</t>
-  </si>
-  <si>
-    <t>발자국은 안쪽 창고로 이어져요. 그런데… 누가 끌려간 흔적은 아니에요.</t>
-  </si>
-  <si>
-    <t>스스로 걸어갔다고?</t>
-  </si>
-  <si>
-    <t>불량한 청년</t>
-  </si>
-  <si>
-    <t>아, 진짜. 난 히어로 같은 거 부른 적 없는데?</t>
-  </si>
-  <si>
-    <t>찾았다! 납치 피해자!</t>
-  </si>
-  <si>
-    <t>피해자 아니거든? 나 이제 빌런 연합 소속이거든?</t>
-  </si>
-  <si>
-    <t>와, 인생 선택지가 저렇게 노골적으로 틀릴 수 있구나.</t>
-  </si>
-  <si>
-    <t>오빠는 빌런 연합에 들어가 한몫 챙기려 했다고 털어놓았다.</t>
-  </si>
-  <si>
-    <t>동생이 널 찾고 있어. 지금이라도 돌아가.</t>
-  </si>
-  <si>
-    <t>웃기지 마. 돌아가면 또 잔소리뿐이야.</t>
-  </si>
-  <si>
-    <t>잔소리할 사람이 있다는 건… 돌아갈 곳이 있다는 뜻 아닐까요?</t>
-  </si>
-  <si>
-    <t>…그런 말로 흔들리지 않거든.</t>
-  </si>
-  <si>
-    <t>주변 빌런부터 제압하고 이야기하자.</t>
-  </si>
-  <si>
-    <t>동네 빌런</t>
-  </si>
-  <si>
-    <t>어이 신입! 저 히어로들 네가 부른 거냐?</t>
-  </si>
-  <si>
-    <t>아, 아니거든요! 저 아직 배신 안 했거든요!</t>
-  </si>
-  <si>
-    <t>약속한 사례를 생각하면, 네가 왜 여기 왔는지 정확히 들어야겠어.</t>
-  </si>
-  <si>
-    <t>사례? 그 꼬맹이가 뭘 준다고 했는데?</t>
-  </si>
-  <si>
-    <t>반짝이는 병뚜껑. 시장 가치가 폭락하기 전에 협조해.</t>
-  </si>
-  <si>
-    <t>그 순간 창고 안쪽에서 빌런들의 고함이 들려왔다.</t>
-  </si>
-  <si>
-    <t>신입은 여기까지다! 공구상 위치를 알았으면 입막음해야지!</t>
-  </si>
-  <si>
-    <t>뭐? 잠깐, 나 아직 정식 계약서도 못 썼는데?</t>
-  </si>
-  <si>
-    <t>오빠는 빌런 연합에게도 버림받은 처지였다.</t>
-  </si>
-  <si>
-    <t>빌런들은 오빠를 묶어 공구상 보강 작업장으로 끌고 갔다.</t>
-  </si>
-  <si>
-    <t>오빠! 오빠 맞죠?!</t>
-  </si>
-  <si>
-    <t>야! 왜 여기까지 왔어! 집에 가라니까!</t>
-  </si>
-  <si>
-    <t>비록 길을 잘못 들었으나, 가족을 걱정하는 마음만은 진짜다!</t>
-  </si>
-  <si>
-    <t>그럼 묶은 줄만 태우면 되지?</t>
-  </si>
-  <si>
-    <t>줄만 태울 수 있어?</t>
-  </si>
-  <si>
-    <t>그런 세세한 주문은 안 받아.</t>
-  </si>
-  <si>
-    <t>그럼 안 돼요! 주변에 기름통이 있어요!</t>
-  </si>
-  <si>
-    <t>구출 방식을 정하자.</t>
-  </si>
-  <si>
-    <t>정면에서 시선을 끌자. 블랙불릿은 오빠를 빼내.</t>
-  </si>
-  <si>
-    <t>좋아. 난 위험한 역할이 제일 싫으니까 빨리 끝낼게.</t>
-  </si>
-  <si>
-    <t>히어로다! 장비부터 챙겨!</t>
-  </si>
-  <si>
-    <t>정면 돌파로 소동이 커졌지만, 오빠를 구출할 틈은 생겼다.</t>
-  </si>
-  <si>
-    <t>빌런들이 버린 작업 동선을 역으로 이용하자.</t>
-  </si>
-  <si>
-    <t>잠깐, 그 길은 공구상 안쪽으로 바로 이어져. 인질들이 있는 쪽이야.</t>
-  </si>
-  <si>
-    <t>그럼 이 정보가 있으면 공구상 인질을 먼저 구할 수 있겠네요!</t>
-  </si>
-  <si>
-    <t>훌륭하다! 잘못을 뉘우치는 마음은 정의로 돌아오는 첫걸음이다!</t>
-  </si>
-  <si>
-    <t>오빠는 소녀에게 잔뜩 혼난 뒤, 공구상 안쪽으로 이어지는 숨은 작업 통로를 알려주었다.</t>
-  </si>
-  <si>
-    <t>나 같은 거 구해줘서… 미안하다. 그리고 고마워.</t>
-  </si>
-  <si>
-    <t>집 가면 엄마한테도 똑같이 말해.</t>
-  </si>
-  <si>
-    <t>소녀와 오빠는 무사히 귀가했고, 오빠는 공구상 안쪽 작업 통로 정보를 넘겨주었다.</t>
-  </si>
-  <si>
-    <t>협회 임시 게시판에 이상한 제보가 붙었다.</t>
-  </si>
-  <si>
-    <t>편의점 점주</t>
-  </si>
-  <si>
-    <t>히어로님들! 우리 가게 진상만 골라 털어가는 빌런이 나타났습니다!</t>
-  </si>
-  <si>
-    <t>진상만?</t>
-  </si>
-  <si>
-    <t>예. 라면 국물 엎고 도망친 손님, 동전 던진 손님, 전부 다음날 지갑이 털렸어요.</t>
-  </si>
-  <si>
-    <t>좋은 사람 아니야?</t>
-  </si>
-  <si>
-    <t>아니다! 사적 제재는 정의가 아니다!</t>
-  </si>
-  <si>
-    <t>조사 방향을 정하자.</t>
-  </si>
-  <si>
-    <t>피해자 영수증과 CCTV 시간부터 대조하자.</t>
-  </si>
-  <si>
-    <t>피해자들이 모두 같은 시간대에 같은 물건을 샀어요. 컵라면, 삼각김밥, 그리고… 진상짓.</t>
-  </si>
-  <si>
-    <t>마지막 품목은 바코드가 없을 텐데.</t>
-  </si>
-  <si>
-    <t>오늘 밤 편의점 앞에서 잠복하자.</t>
-  </si>
-  <si>
-    <t>좋아. 진상이 오면 내가 먼저 화를 내도 돼?</t>
-  </si>
-  <si>
-    <t>그럼 잠복이 아니라 사건 현장 재현이야.</t>
-  </si>
-  <si>
-    <t>빌런이면 일단 잡고 보자.</t>
-  </si>
-  <si>
-    <t>그 기백은 훌륭하나, 범인을 모르면 잡을 수도 없다!</t>
-  </si>
-  <si>
-    <t>조사 끝에 범인이 편의점 진상들의 동선을 미리 알고 움직인다는 사실을 알아냈다.</t>
-  </si>
-  <si>
-    <t>히어로들은 편의점 빌런이 남긴 검은 명단을 따라 오로라 골목을 추적했다.</t>
-  </si>
-  <si>
-    <t>명단에 피해자 이름 옆으로 별점이 있어요.</t>
-  </si>
-  <si>
-    <t>진상 등급표네. 별 다섯 개는 뭘 해야 받는 거야?</t>
-  </si>
-  <si>
-    <t>전자레인지에 생달걀을 넣고 터뜨린 손님입니다.</t>
-  </si>
-  <si>
-    <t>그건 빌런 맞지 않아?</t>
-  </si>
-  <si>
-    <t>그래도 우리가 잡아야 할 건 편의점 빌런이야.</t>
-  </si>
-  <si>
-    <t>명단 뒤에는 빌런 연합의 물자 이동 시간표가 작게 적혀 있었다.</t>
-  </si>
-  <si>
-    <t>이 사람, 진상만 쫓은 게 아니라 빌런 물자까지 훔치고 있었어요.</t>
-  </si>
-  <si>
-    <t>추적 방법을 정하자.</t>
-  </si>
-  <si>
-    <t>명단의 다음 표적을 보호하며 기다리자.</t>
-  </si>
-  <si>
-    <t>보호 대상이 별 다섯 개 진상인 건 조금 고통스럽네.</t>
-  </si>
-  <si>
-    <t>편의점 직원들에게 범인의 습관을 묻자.</t>
-  </si>
-  <si>
-    <t>전직 알바생</t>
-  </si>
-  <si>
-    <t>범인은 꼭 계산대 앞에서 '어서오세요'를 혼잣말로 해요. 버릇처럼요.</t>
-  </si>
-  <si>
-    <t>그 말엔 슬픔이 묻어 있군.</t>
-  </si>
-  <si>
-    <t>추적 끝에 편의점 빌런이 버려진 무인 편의점에 숨어 있다는 사실을 알아냈다.</t>
-  </si>
-  <si>
-    <t>버려진 무인 편의점 안에는 빼곡한 진상 명단과 빌런 연합 물자 상자가 쌓여 있었다.</t>
-  </si>
-  <si>
-    <t>편의점 빌런</t>
-  </si>
-  <si>
-    <t>어서오세요. 아니, 오지 마세요. 당신들은 어떤 진상입니까?</t>
-  </si>
-  <si>
-    <t>우린 히어로다.</t>
-  </si>
-  <si>
-    <t>히어로? 제가 되고 싶었던 바로 그 직업이군요.</t>
-  </si>
-  <si>
-    <t>하지만 협회는 제 이상을 거절했습니다. 모든 진상을 구축하겠다는 숭고한 꿈을요.</t>
-  </si>
-  <si>
-    <t>협회가 의외로 정상적인 판단을 했네.</t>
-  </si>
-  <si>
-    <t>그래서 제가 직접 세상을 정화하기로 했습니다. 시민도, 빌런도, 진상이라면 예외 없습니다.</t>
-  </si>
-  <si>
-    <t>그건 정의가 아니다. 분노에 이름표를 붙였을 뿐이다!</t>
-  </si>
-  <si>
-    <t>대응을 정하자.</t>
-  </si>
-  <si>
-    <t>당장 제압한다. 더 피해가 나기 전에 끝내자.</t>
-  </si>
-  <si>
-    <t>진상을 감싸는 자도 진상입니다!</t>
-  </si>
-  <si>
-    <t>편의점 빌런은 계산대 바코드 스캐너를 검처럼 들고 달려들었다.</t>
-  </si>
-  <si>
-    <t>네가 겪은 일은 알겠어. 하지만 그걸로 남을 해칠 권리는 없어.</t>
-  </si>
-  <si>
-    <t>권리요? 진상들은 제게 그런 걸 묻지 않았습니다.</t>
-  </si>
-  <si>
-    <t>그래도 누군가를 다치게 하면, 당신도 똑같이 누군가의 공포가 돼요.</t>
-  </si>
-  <si>
-    <t>…그 말, 교대 근무 끝나고 들었으면 조금 위로가 됐겠네요.</t>
-  </si>
-  <si>
-    <t>저스티스, 전직 히어로 지망생으로서 면접을 다시 봐줘.</t>
-  </si>
-  <si>
-    <t>좋다! 첫 질문이다. 진상이란 무엇인가!</t>
-  </si>
-  <si>
-    <t>그 면접, 오늘 안에 끝나긴 해?</t>
-  </si>
-  <si>
-    <t>격전 끝에 편의점 빌런은 제압되었고, 그가 모은 빌런 연합 은닉 자원 위치 정보가 확보되었다.</t>
-  </si>
-  <si>
-    <t>그 자료는… 진상을 막기 위해 모은 겁니다. 부디 제대로 써주세요.</t>
-  </si>
-  <si>
-    <t>그래. 적어도 네가 못 이룬 좋은 일에는 쓰이게 할게.</t>
-  </si>
-  <si>
-    <t>오로라 1구역의 숨겨진 자원 구역 일부가 지도에 표시되었다.</t>
-  </si>
-  <si>
-    <t>Set_Flag_SubEvent1Accept</t>
-  </si>
-  <si>
-    <t>서브 이벤트1_1 수락</t>
-  </si>
-  <si>
-    <t>Set_Flag_SubEvent1RewardDemand</t>
-  </si>
-  <si>
-    <t>보상 요구 루트</t>
-  </si>
-  <si>
-    <t>Set_Flag_SubEvent1Start</t>
-  </si>
-  <si>
-    <t>오빠 추적 시작</t>
-  </si>
-  <si>
-    <t>Set_Flag_BrotherPersuade</t>
-  </si>
-  <si>
-    <t>설득 루트</t>
-  </si>
-  <si>
-    <t>Start_Battle_1050</t>
-  </si>
-  <si>
-    <t>골목 빌런전</t>
-  </si>
-  <si>
-    <t>Flag_SubEvent1RewardDemand==1</t>
-  </si>
-  <si>
-    <t>약속한 사례부터 확인한다.</t>
-  </si>
-  <si>
-    <t>보상 요구 선택 시 노출</t>
-  </si>
-  <si>
-    <t>Set_Flag_SubEvent1Truth</t>
-  </si>
-  <si>
-    <t>오빠의 진실 확인</t>
-  </si>
-  <si>
-    <t>Start_Battle_1060</t>
-  </si>
-  <si>
-    <t>정면 구출</t>
-  </si>
-  <si>
-    <t>Flag_SubEvent1Truth==1</t>
-  </si>
-  <si>
-    <t>서브 이벤트1 내부 단서 활용</t>
-  </si>
-  <si>
-    <t>Flag_1SectorMainEventClear==1</t>
-  </si>
-  <si>
-    <t>메인 이벤트 클리어 후 완료 보상 대체</t>
-  </si>
-  <si>
-    <t>서브 이벤트1 완료: 공구상 인질 구출 히든 루트 해금</t>
-  </si>
-  <si>
-    <t>단서 조사</t>
-  </si>
-  <si>
-    <t>잠복 조사</t>
-  </si>
-  <si>
-    <t>무작정 수색</t>
-  </si>
-  <si>
-    <t>Set_Flag_SubEvent2Start</t>
-  </si>
-  <si>
-    <t>편의점 빌런 추적 시작</t>
-  </si>
-  <si>
-    <t>표적 보호</t>
-  </si>
-  <si>
-    <t>직원 탐문</t>
-  </si>
-  <si>
-    <t>Set_Flag_SubEvent2TraceComplete</t>
-  </si>
-  <si>
-    <t>은신처 발견</t>
-  </si>
-  <si>
-    <t>Start_Battle_1080</t>
-  </si>
-  <si>
-    <t>편의점 빌런전</t>
-  </si>
-  <si>
-    <t>설득 시도</t>
-  </si>
-  <si>
-    <t>Stat</t>
-  </si>
-  <si>
-    <t>Justice_IP &gt;= 30</t>
-  </si>
-  <si>
-    <t>저스티스 I.P 조건</t>
-  </si>
-  <si>
-    <t>서브 이벤트2 완료</t>
-  </si>
-  <si>
-    <t>Set_Flag_SubEvent1Complete\
-Reward_AllHeroIP_001</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>Set_Flag_SubEvent1Complete\
-Set_Flag_1CectorHiddenRoute\
-Reward_1SectorHiddenRoute</t>
+    <t>HostageInjuredCount &gt;= 1
+HostageInjuredCount &lt;= 2</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>Set_Flag_SubEvent2Complete\
-Reward_AllHeroIP_002</t>
+    <t>Flag\
+Flag</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>Set_Flag_SubEvent2Complete\
-Reveal_Fog_Level2\
-Reward_1SectorHiddenResource</t>
+    <t>몰래 들어갈 곳을 찾아보자</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
   <si>
-    <t>집 나간 오빠의 진상 파악</t>
+    <t>우선 인질부터 구출하자.</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -2065,7 +2072,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="20">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2089,48 +2096,47 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Pretendard Medium"/>
-      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Pretendard Medium"/>
-      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Pretendard ExtraBold"/>
-      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Pretendard Medium"/>
-      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
       <name val="Pretendard Medium"/>
-      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="16"/>
       <color theme="1"/>
       <name val="Pretendard Medium"/>
-      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="Pretendard Medium"/>
-      <family val="2"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
@@ -2303,7 +2309,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2407,17 +2413,32 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -2431,21 +2452,10 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="보통" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -2795,141 +2805,141 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:L58"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12.25" customWidth="1"/>
-    <col min="3" max="3" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
     <col min="4" max="4" width="12.25" customWidth="1"/>
-    <col min="5" max="5" width="46.83203125" customWidth="1"/>
+    <col min="5" max="5" width="46.875" customWidth="1"/>
     <col min="6" max="6" width="37.75" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.375" customWidth="1"/>
     <col min="9" max="9" width="10.5" customWidth="1"/>
-    <col min="10" max="10" width="41.08203125" customWidth="1"/>
-    <col min="14" max="14" width="11.58203125" customWidth="1"/>
-    <col min="17" max="17" width="75.33203125" customWidth="1"/>
+    <col min="10" max="10" width="41.125" customWidth="1"/>
+    <col min="14" max="14" width="11.625" customWidth="1"/>
+    <col min="17" max="17" width="75.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12">
-      <c r="B2" s="53" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" s="53"/>
-      <c r="D2" s="53"/>
-      <c r="E2" s="53"/>
-      <c r="F2" s="53"/>
-      <c r="G2" s="53"/>
-      <c r="H2" s="53"/>
-      <c r="I2" s="53"/>
-      <c r="J2" s="53"/>
-      <c r="K2" s="53"/>
-      <c r="L2" s="53"/>
-    </row>
-    <row r="3" spans="2:12">
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
-      <c r="I3" s="53"/>
-      <c r="J3" s="53"/>
-      <c r="K3" s="53"/>
-      <c r="L3" s="53"/>
-    </row>
-    <row r="4" spans="2:12">
-      <c r="B4" s="53"/>
-      <c r="C4" s="53"/>
-      <c r="D4" s="53"/>
-      <c r="E4" s="53"/>
-      <c r="F4" s="53"/>
-      <c r="G4" s="53"/>
-      <c r="H4" s="53"/>
-      <c r="I4" s="53"/>
-      <c r="J4" s="53"/>
-      <c r="K4" s="53"/>
-      <c r="L4" s="53"/>
-    </row>
-    <row r="5" spans="2:12">
-      <c r="B5" s="53"/>
-      <c r="C5" s="53"/>
-      <c r="D5" s="53"/>
-      <c r="E5" s="53"/>
-      <c r="F5" s="53"/>
-      <c r="G5" s="53"/>
-      <c r="H5" s="53"/>
-      <c r="I5" s="53"/>
-      <c r="J5" s="53"/>
-      <c r="K5" s="53"/>
-      <c r="L5" s="53"/>
-    </row>
-    <row r="6" spans="2:12">
-      <c r="B6" s="53"/>
-      <c r="C6" s="53"/>
-      <c r="D6" s="53"/>
-      <c r="E6" s="53"/>
-      <c r="F6" s="53"/>
-      <c r="G6" s="53"/>
-      <c r="H6" s="53"/>
-      <c r="I6" s="53"/>
-      <c r="J6" s="53"/>
-      <c r="K6" s="53"/>
-      <c r="L6" s="53"/>
-    </row>
-    <row r="7" spans="2:12">
-      <c r="B7" s="53"/>
-      <c r="C7" s="53"/>
-      <c r="D7" s="53"/>
-      <c r="E7" s="53"/>
-      <c r="F7" s="53"/>
-      <c r="G7" s="53"/>
-      <c r="H7" s="53"/>
-      <c r="I7" s="53"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="53"/>
-      <c r="L7" s="53"/>
-    </row>
-    <row r="8" spans="2:12">
-      <c r="B8" s="53"/>
-      <c r="C8" s="53"/>
-      <c r="D8" s="53"/>
-      <c r="E8" s="53"/>
-      <c r="F8" s="53"/>
-      <c r="G8" s="53"/>
-      <c r="H8" s="53"/>
-      <c r="I8" s="53"/>
-      <c r="J8" s="53"/>
-      <c r="K8" s="53"/>
-      <c r="L8" s="53"/>
-    </row>
-    <row r="9" spans="2:12">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="53"/>
-      <c r="E9" s="53"/>
-      <c r="F9" s="53"/>
-      <c r="G9" s="53"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="53"/>
-      <c r="J9" s="53"/>
-      <c r="K9" s="53"/>
-      <c r="L9" s="53"/>
-    </row>
-    <row r="10" spans="2:12">
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="53"/>
-      <c r="H10" s="53"/>
-      <c r="I10" s="53"/>
-      <c r="J10" s="53"/>
-      <c r="K10" s="53"/>
-      <c r="L10" s="53"/>
-    </row>
-    <row r="11" spans="2:12">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B2" s="48" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="48"/>
+      <c r="D2" s="48"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="48"/>
+      <c r="G2" s="48"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="48"/>
+      <c r="J2" s="48"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="48"/>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B3" s="48"/>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+      <c r="H3" s="48"/>
+      <c r="I3" s="48"/>
+      <c r="J3" s="48"/>
+      <c r="K3" s="48"/>
+      <c r="L3" s="48"/>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="48"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="48"/>
+      <c r="C5" s="48"/>
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="48"/>
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="I5" s="48"/>
+      <c r="J5" s="48"/>
+      <c r="K5" s="48"/>
+      <c r="L5" s="48"/>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="I6" s="48"/>
+      <c r="J6" s="48"/>
+      <c r="K6" s="48"/>
+      <c r="L6" s="48"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="48"/>
+      <c r="K7" s="48"/>
+      <c r="L7" s="48"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="48"/>
+      <c r="C8" s="48"/>
+      <c r="D8" s="48"/>
+      <c r="E8" s="48"/>
+      <c r="F8" s="48"/>
+      <c r="G8" s="48"/>
+      <c r="H8" s="48"/>
+      <c r="I8" s="48"/>
+      <c r="J8" s="48"/>
+      <c r="K8" s="48"/>
+      <c r="L8" s="48"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="48"/>
+      <c r="K9" s="48"/>
+      <c r="L9" s="48"/>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B10" s="48"/>
+      <c r="C10" s="48"/>
+      <c r="D10" s="48"/>
+      <c r="E10" s="48"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="48"/>
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="48"/>
+      <c r="K10" s="48"/>
+      <c r="L10" s="48"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -2942,7 +2952,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
     </row>
-    <row r="12" spans="2:12">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
@@ -2955,75 +2965,75 @@
       <c r="K12" s="1"/>
       <c r="L12" s="1"/>
     </row>
-    <row r="13" spans="2:12">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="52" t="s">
+      <c r="C13" s="47" t="s">
         <v>2</v>
       </c>
-      <c r="D13" s="52"/>
-      <c r="E13" s="52"/>
-      <c r="F13" s="52"/>
-      <c r="G13" s="52"/>
-      <c r="H13" s="52"/>
-      <c r="I13" s="52"/>
-      <c r="J13" s="52"/>
-      <c r="K13" s="52"/>
-      <c r="L13" s="52"/>
-    </row>
-    <row r="14" spans="2:12">
+      <c r="D13" s="47"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="47"/>
+      <c r="G13" s="47"/>
+      <c r="H13" s="47"/>
+      <c r="I13" s="47"/>
+      <c r="J13" s="47"/>
+      <c r="K13" s="47"/>
+      <c r="L13" s="47"/>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C14" s="52" t="s">
+      <c r="C14" s="47" t="s">
         <v>4</v>
       </c>
-      <c r="D14" s="52"/>
-      <c r="E14" s="52"/>
-      <c r="F14" s="52"/>
-      <c r="G14" s="52"/>
-      <c r="H14" s="52"/>
-      <c r="I14" s="52"/>
-      <c r="J14" s="52"/>
-      <c r="K14" s="52"/>
-      <c r="L14" s="52"/>
-    </row>
-    <row r="15" spans="2:12">
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+      <c r="I14" s="47"/>
+      <c r="J14" s="47"/>
+      <c r="K14" s="47"/>
+      <c r="L14" s="47"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="52" t="s">
+      <c r="C15" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="D15" s="52"/>
-      <c r="E15" s="52"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="52"/>
-      <c r="H15" s="52"/>
-      <c r="I15" s="52"/>
-      <c r="J15" s="52"/>
-      <c r="K15" s="52"/>
-      <c r="L15" s="52"/>
-    </row>
-    <row r="16" spans="2:12" ht="91.5" customHeight="1">
+      <c r="D15" s="47"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="47"/>
+      <c r="G15" s="47"/>
+      <c r="H15" s="47"/>
+      <c r="I15" s="47"/>
+      <c r="J15" s="47"/>
+      <c r="K15" s="47"/>
+      <c r="L15" s="47"/>
+    </row>
+    <row r="16" spans="2:12" ht="91.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C16" s="49" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="54"/>
-      <c r="E16" s="54"/>
-      <c r="F16" s="54"/>
-      <c r="G16" s="54"/>
-      <c r="H16" s="54"/>
-      <c r="I16" s="54"/>
-      <c r="J16" s="54"/>
-      <c r="K16" s="54"/>
-      <c r="L16" s="54"/>
-    </row>
-    <row r="17" spans="2:12">
+      <c r="D16" s="49"/>
+      <c r="E16" s="49"/>
+      <c r="F16" s="49"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="49"/>
+      <c r="I16" s="49"/>
+      <c r="J16" s="49"/>
+      <c r="K16" s="49"/>
+      <c r="L16" s="49"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" s="35"/>
       <c r="C17" s="36"/>
       <c r="D17" s="36"/>
@@ -3036,7 +3046,7 @@
       <c r="K17" s="36"/>
       <c r="L17" s="36"/>
     </row>
-    <row r="18" spans="2:12">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" s="3" t="s">
         <v>9</v>
       </c>
@@ -3059,7 +3069,7 @@
       <c r="K18" s="36"/>
       <c r="L18" s="36"/>
     </row>
-    <row r="19" spans="2:12">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" s="34">
         <v>46206</v>
       </c>
@@ -3080,7 +3090,7 @@
       <c r="K19" s="36"/>
       <c r="L19" s="36"/>
     </row>
-    <row r="20" spans="2:12">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B20" s="34">
         <v>46213</v>
       </c>
@@ -3101,7 +3111,7 @@
       <c r="K20" s="36"/>
       <c r="L20" s="36"/>
     </row>
-    <row r="21" spans="2:12">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B21" s="34">
         <v>46213</v>
       </c>
@@ -3124,21 +3134,21 @@
       <c r="K21" s="36"/>
       <c r="L21" s="36"/>
     </row>
-    <row r="22" spans="2:12">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B22" s="34">
         <v>46213</v>
       </c>
       <c r="C22" s="39" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="D22" s="39" t="s">
         <v>15</v>
       </c>
       <c r="E22" s="39" t="s">
+        <v>410</v>
+      </c>
+      <c r="F22" s="39" t="s">
         <v>411</v>
-      </c>
-      <c r="F22" s="39" t="s">
-        <v>412</v>
       </c>
       <c r="G22" s="36"/>
       <c r="H22" s="36"/>
@@ -3147,7 +3157,7 @@
       <c r="K22" s="36"/>
       <c r="L22" s="36"/>
     </row>
-    <row r="23" spans="2:12">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B23" s="35"/>
       <c r="C23" s="36"/>
       <c r="D23" s="36"/>
@@ -3160,12 +3170,12 @@
       <c r="K23" s="36"/>
       <c r="L23" s="36"/>
     </row>
-    <row r="26" spans="2:12" ht="25.5">
+    <row r="26" spans="2:12" ht="26.25" x14ac:dyDescent="0.5">
       <c r="B26" s="24" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="2:12" ht="21" thickBot="1">
+    <row r="28" spans="2:12" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B28" s="20" t="s">
         <v>24</v>
       </c>
@@ -3175,7 +3185,7 @@
       <c r="D28" s="17"/>
       <c r="E28" s="17"/>
     </row>
-    <row r="29" spans="2:12" ht="17.5" thickBot="1">
+    <row r="29" spans="2:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="7" t="s">
         <v>28</v>
       </c>
@@ -3189,7 +3199,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="2:12" ht="106.5" customHeight="1" thickBot="1">
+    <row r="30" spans="2:12" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="7" t="s">
         <v>32</v>
       </c>
@@ -3203,53 +3213,53 @@
         <v>35</v>
       </c>
     </row>
-    <row r="31" spans="2:12">
-      <c r="B31" s="45" t="s">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B31" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="C31" s="45" t="s">
+      <c r="C31" s="44" t="s">
         <v>41</v>
       </c>
-      <c r="D31" s="45" t="s">
+      <c r="D31" s="44" t="s">
         <v>34</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="2:12">
-      <c r="B32" s="51"/>
-      <c r="C32" s="51"/>
-      <c r="D32" s="51"/>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="B32" s="45"/>
+      <c r="C32" s="45"/>
+      <c r="D32" s="45"/>
       <c r="E32" s="9" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="33" spans="2:5">
-      <c r="B33" s="51"/>
-      <c r="C33" s="51"/>
-      <c r="D33" s="51"/>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="45"/>
+      <c r="C33" s="45"/>
+      <c r="D33" s="45"/>
       <c r="E33" s="9" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="34" spans="2:5">
-      <c r="B34" s="51"/>
-      <c r="C34" s="51"/>
-      <c r="D34" s="51"/>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="45"/>
+      <c r="C34" s="45"/>
+      <c r="D34" s="45"/>
       <c r="E34" s="10" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="35" spans="2:5">
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="45"/>
+      <c r="C35" s="45"/>
+      <c r="D35" s="45"/>
       <c r="E35" s="9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="2:5" ht="17.5" thickBot="1">
+    <row r="36" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="46"/>
       <c r="C36" s="46"/>
       <c r="D36" s="46"/>
@@ -3257,7 +3267,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="37" spans="2:5" ht="17.5" thickBot="1">
+    <row r="37" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="7" t="s">
         <v>61</v>
       </c>
@@ -3271,7 +3281,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="38" spans="2:5" ht="17.5" thickBot="1">
+    <row r="38" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="7" t="s">
         <v>65</v>
       </c>
@@ -3285,7 +3295,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="17.5" thickBot="1">
+    <row r="39" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="7" t="s">
         <v>71</v>
       </c>
@@ -3299,7 +3309,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="40" spans="2:5" ht="17.5" thickBot="1">
+    <row r="40" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B40" s="7" t="s">
         <v>78</v>
       </c>
@@ -3313,7 +3323,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="41" spans="2:5" ht="17.5" thickBot="1">
+    <row r="41" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B41" s="7" t="s">
         <v>84</v>
       </c>
@@ -3327,7 +3337,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="42" spans="2:5" ht="17.5" thickBot="1">
+    <row r="42" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B42" s="7" t="s">
         <v>88</v>
       </c>
@@ -3341,13 +3351,13 @@
         <v>90</v>
       </c>
     </row>
-    <row r="43" spans="2:5" ht="284.25" customHeight="1"/>
-    <row r="44" spans="2:5">
+    <row r="43" spans="2:5" ht="284.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44" s="23" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="45" spans="2:5" ht="21" thickBot="1">
+    <row r="45" spans="2:5" ht="21" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B45" s="20" t="s">
         <v>26</v>
       </c>
@@ -3355,7 +3365,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="46" spans="2:5" ht="17.5" thickBot="1">
+    <row r="46" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B46" s="5" t="s">
         <v>28</v>
       </c>
@@ -3369,7 +3379,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="47" spans="2:5" ht="98.5" thickBot="1">
+    <row r="47" spans="2:5" ht="105.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="7" t="s">
         <v>36</v>
       </c>
@@ -3383,7 +3393,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="48" spans="2:5" ht="17.5" thickBot="1">
+    <row r="48" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B48" s="7" t="s">
         <v>43</v>
       </c>
@@ -3397,67 +3407,67 @@
         <v>45</v>
       </c>
     </row>
-    <row r="49" spans="2:5">
-      <c r="B49" s="43" t="s">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B49" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="C49" s="47" t="s">
+      <c r="C49" s="52" t="s">
         <v>48</v>
       </c>
-      <c r="D49" s="47" t="s">
+      <c r="D49" s="52" t="s">
         <v>49</v>
       </c>
       <c r="E49" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="50" spans="2:5">
-      <c r="B50" s="50"/>
-      <c r="C50" s="48"/>
-      <c r="D50" s="48"/>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B50" s="55"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
       <c r="E50" s="18" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="51" spans="2:5">
-      <c r="B51" s="50"/>
-      <c r="C51" s="48"/>
-      <c r="D51" s="48"/>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B51" s="55"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
       <c r="E51" s="18" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="2:5" ht="17.5" thickBot="1">
-      <c r="B52" s="44"/>
-      <c r="C52" s="49"/>
-      <c r="D52" s="49"/>
+    <row r="52" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B52" s="51"/>
+      <c r="C52" s="54"/>
+      <c r="D52" s="54"/>
       <c r="E52" s="19" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="53" spans="2:5">
-      <c r="B53" s="43" t="s">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B53" s="50" t="s">
         <v>57</v>
       </c>
-      <c r="C53" s="47" t="s">
+      <c r="C53" s="52" t="s">
         <v>58</v>
       </c>
-      <c r="D53" s="47" t="s">
+      <c r="D53" s="52" t="s">
         <v>59</v>
       </c>
       <c r="E53" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="54" spans="2:5" ht="17.5" thickBot="1">
-      <c r="B54" s="44"/>
-      <c r="C54" s="49"/>
-      <c r="D54" s="49"/>
+    <row r="54" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B54" s="51"/>
+      <c r="C54" s="54"/>
+      <c r="D54" s="54"/>
       <c r="E54" s="12" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="55" spans="2:5" ht="28.5" thickBot="1">
+    <row r="55" spans="2:5" ht="30.75" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B55" s="7" t="s">
         <v>68</v>
       </c>
@@ -3471,7 +3481,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="56" spans="2:5" ht="17.5" thickBot="1">
+    <row r="56" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B56" s="7" t="s">
         <v>74</v>
       </c>
@@ -3485,22 +3495,22 @@
         <v>77</v>
       </c>
     </row>
-    <row r="57" spans="2:5">
-      <c r="B57" s="43" t="s">
+    <row r="57" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B57" s="50" t="s">
         <v>81</v>
       </c>
-      <c r="C57" s="45" t="s">
+      <c r="C57" s="44" t="s">
         <v>82</v>
       </c>
-      <c r="D57" s="45" t="s">
+      <c r="D57" s="44" t="s">
         <v>59</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="58" spans="2:5" ht="17.5" thickBot="1">
-      <c r="B58" s="44"/>
+    <row r="58" spans="2:5" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B58" s="51"/>
       <c r="C58" s="46"/>
       <c r="D58" s="46"/>
       <c r="E58" s="12" t="s">
@@ -3509,14 +3519,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="B31:B36"/>
-    <mergeCell ref="C31:C36"/>
-    <mergeCell ref="D31:D36"/>
-    <mergeCell ref="C13:L13"/>
-    <mergeCell ref="B2:L10"/>
-    <mergeCell ref="C14:L14"/>
-    <mergeCell ref="C15:L15"/>
-    <mergeCell ref="C16:L16"/>
     <mergeCell ref="B57:B58"/>
     <mergeCell ref="C57:C58"/>
     <mergeCell ref="D57:D58"/>
@@ -3526,6 +3528,14 @@
     <mergeCell ref="B53:B54"/>
     <mergeCell ref="C53:C54"/>
     <mergeCell ref="D53:D54"/>
+    <mergeCell ref="B31:B36"/>
+    <mergeCell ref="C31:C36"/>
+    <mergeCell ref="D31:D36"/>
+    <mergeCell ref="C13:L13"/>
+    <mergeCell ref="B2:L10"/>
+    <mergeCell ref="C14:L14"/>
+    <mergeCell ref="C15:L15"/>
+    <mergeCell ref="C16:L16"/>
   </mergeCells>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3537,15 +3547,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:E11"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="13.5" customWidth="1"/>
-    <col min="3" max="3" width="11.58203125" customWidth="1"/>
+    <col min="3" max="3" width="11.625" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
     <col min="5" max="5" width="89.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:5">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>91</v>
       </c>
@@ -3559,7 +3569,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="3" spans="2:5" ht="34">
+    <row r="3" spans="2:5" ht="33" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>95</v>
       </c>
@@ -3573,8 +3583,8 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="2:5">
-      <c r="B4" s="55" t="s">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="56" t="s">
         <v>99</v>
       </c>
       <c r="C4" t="s">
@@ -3587,8 +3597,8 @@
         <v>102</v>
       </c>
     </row>
-    <row r="5" spans="2:5" ht="68">
-      <c r="B5" s="55"/>
+    <row r="5" spans="2:5" ht="66" x14ac:dyDescent="0.3">
+      <c r="B5" s="56"/>
       <c r="C5" t="s">
         <v>103</v>
       </c>
@@ -3599,8 +3609,8 @@
         <v>105</v>
       </c>
     </row>
-    <row r="6" spans="2:5">
-      <c r="B6" s="55" t="s">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="56" t="s">
         <v>106</v>
       </c>
       <c r="C6" t="s">
@@ -3613,8 +3623,8 @@
         <v>109</v>
       </c>
     </row>
-    <row r="7" spans="2:5">
-      <c r="B7" s="55"/>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="56"/>
       <c r="C7" t="s">
         <v>110</v>
       </c>
@@ -3622,11 +3632,11 @@
         <v>111</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="8" spans="2:5">
-      <c r="B8" s="55"/>
+        <v>600</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="56"/>
       <c r="C8" t="s">
         <v>112</v>
       </c>
@@ -3637,8 +3647,8 @@
         <v>114</v>
       </c>
     </row>
-    <row r="9" spans="2:5">
-      <c r="B9" s="55" t="s">
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="56" t="s">
         <v>115</v>
       </c>
       <c r="C9" t="s">
@@ -3651,8 +3661,8 @@
         <v>118</v>
       </c>
     </row>
-    <row r="10" spans="2:5">
-      <c r="B10" s="55"/>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="56"/>
       <c r="C10" t="s">
         <v>119</v>
       </c>
@@ -3663,8 +3673,8 @@
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="2:5">
-      <c r="B11" s="55"/>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="56"/>
       <c r="C11" t="s">
         <v>122</v>
       </c>
@@ -3689,19 +3699,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:H280"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.58203125" customWidth="1"/>
+    <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="10.25" customWidth="1"/>
     <col min="3" max="3" width="16.5" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="109.25" customWidth="1"/>
-    <col min="6" max="6" width="27.58203125" customWidth="1"/>
-    <col min="7" max="7" width="14.08203125" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="27.625" customWidth="1"/>
+    <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="8" max="8" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>33</v>
       </c>
@@ -3727,7 +3737,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>1020010</v>
       </c>
@@ -3745,7 +3755,7 @@
       </c>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>1020020</v>
       </c>
@@ -3763,7 +3773,7 @@
       </c>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>1020030</v>
       </c>
@@ -3783,7 +3793,7 @@
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>1020040</v>
       </c>
@@ -3801,7 +3811,7 @@
       </c>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>1020050</v>
       </c>
@@ -3821,7 +3831,7 @@
       </c>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>1020060</v>
       </c>
@@ -3839,7 +3849,7 @@
       </c>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>1020070</v>
       </c>
@@ -3859,7 +3869,7 @@
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>1020080</v>
       </c>
@@ -3877,7 +3887,7 @@
       </c>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>1020090</v>
       </c>
@@ -3895,7 +3905,7 @@
       </c>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>1020100</v>
       </c>
@@ -3915,7 +3925,7 @@
       </c>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>1020110</v>
       </c>
@@ -3935,7 +3945,7 @@
       </c>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>1020120</v>
       </c>
@@ -3955,7 +3965,7 @@
       </c>
       <c r="H13" s="3"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>1020130</v>
       </c>
@@ -3973,7 +3983,7 @@
       </c>
       <c r="H14" s="3"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>1020140</v>
       </c>
@@ -3991,7 +4001,7 @@
       </c>
       <c r="H15" s="3"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>1020150</v>
       </c>
@@ -4011,7 +4021,7 @@
       </c>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>1020160</v>
       </c>
@@ -4031,7 +4041,7 @@
       </c>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>1020170</v>
       </c>
@@ -4051,7 +4061,7 @@
       </c>
       <c r="H18" s="3"/>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>1020180</v>
       </c>
@@ -4069,7 +4079,7 @@
         <v>10101</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>1020190</v>
       </c>
@@ -4087,7 +4097,7 @@
       </c>
       <c r="H20" s="3"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>1020200</v>
       </c>
@@ -4107,7 +4117,7 @@
       </c>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>1020210</v>
       </c>
@@ -4127,7 +4137,7 @@
       </c>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="3">
         <v>1020220</v>
       </c>
@@ -4147,7 +4157,7 @@
       </c>
       <c r="H23" s="3"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="3">
         <v>1020230</v>
       </c>
@@ -4167,7 +4177,7 @@
       </c>
       <c r="H24" s="3"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="3">
         <v>1020240</v>
       </c>
@@ -4187,7 +4197,7 @@
       </c>
       <c r="H25" s="3"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="3">
         <v>1020250</v>
       </c>
@@ -4205,7 +4215,7 @@
       </c>
       <c r="H26" s="3"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="3">
         <v>1020260</v>
       </c>
@@ -4223,7 +4233,7 @@
       </c>
       <c r="H27" s="3"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="3">
         <v>1020270</v>
       </c>
@@ -4241,7 +4251,7 @@
       </c>
       <c r="H28" s="3"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="3">
         <v>1020280</v>
       </c>
@@ -4261,7 +4271,7 @@
       </c>
       <c r="H29" s="3"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="3">
         <v>1020290</v>
       </c>
@@ -4279,7 +4289,7 @@
       </c>
       <c r="H30" s="3"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="3">
         <v>1020300</v>
       </c>
@@ -4299,7 +4309,7 @@
       </c>
       <c r="H31" s="3"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="3">
         <v>1020310</v>
       </c>
@@ -4319,7 +4329,7 @@
       </c>
       <c r="H32" s="3"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="3">
         <v>1020320</v>
       </c>
@@ -4337,7 +4347,7 @@
       </c>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="3">
         <v>1020330</v>
       </c>
@@ -4355,7 +4365,7 @@
       </c>
       <c r="H34" s="3"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="3">
         <v>1020340</v>
       </c>
@@ -4373,7 +4383,7 @@
       </c>
       <c r="H35" s="3"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="3">
         <v>1020350</v>
       </c>
@@ -4389,7 +4399,7 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="25">
         <v>1030010</v>
       </c>
@@ -4409,7 +4419,7 @@
       </c>
       <c r="H37" s="3"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="25">
         <v>1030020</v>
       </c>
@@ -4429,7 +4439,7 @@
       </c>
       <c r="H38" s="3"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="25">
         <v>1030030</v>
       </c>
@@ -4447,7 +4457,7 @@
       </c>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="25">
         <v>1030040</v>
       </c>
@@ -4467,7 +4477,7 @@
       </c>
       <c r="H40" s="3"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="25">
         <v>1030050</v>
       </c>
@@ -4487,7 +4497,7 @@
       </c>
       <c r="H41" s="3"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="25">
         <v>1030060</v>
       </c>
@@ -4505,7 +4515,7 @@
       </c>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="25">
         <v>1030070</v>
       </c>
@@ -4523,7 +4533,7 @@
       </c>
       <c r="H43" s="3"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="25">
         <v>1030080</v>
       </c>
@@ -4543,7 +4553,7 @@
       </c>
       <c r="H44" s="3"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="25">
         <v>1030090</v>
       </c>
@@ -4563,7 +4573,7 @@
       </c>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="25">
         <v>1030100</v>
       </c>
@@ -4581,7 +4591,7 @@
       </c>
       <c r="H46" s="3"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="25">
         <v>1030110</v>
       </c>
@@ -4601,7 +4611,7 @@
       </c>
       <c r="H47" s="3"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="25">
         <v>1030120</v>
       </c>
@@ -4621,7 +4631,7 @@
       </c>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="25">
         <v>1030130</v>
       </c>
@@ -4639,7 +4649,7 @@
         <v>10201</v>
       </c>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="25">
         <v>1030140</v>
       </c>
@@ -4657,7 +4667,7 @@
       </c>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="25">
         <v>1030150</v>
       </c>
@@ -4677,7 +4687,7 @@
       </c>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="25">
         <v>1030160</v>
       </c>
@@ -4697,7 +4707,7 @@
       </c>
       <c r="H52" s="3"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="25">
         <v>1030170</v>
       </c>
@@ -4717,7 +4727,7 @@
         <v>10202</v>
       </c>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="25">
         <v>1030180</v>
       </c>
@@ -4733,7 +4743,7 @@
       </c>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="25">
         <v>1030190</v>
       </c>
@@ -4753,7 +4763,7 @@
         <v>10203</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="25">
         <v>1030200</v>
       </c>
@@ -4773,7 +4783,7 @@
       </c>
       <c r="H56" s="3"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="25">
         <v>1030210</v>
       </c>
@@ -4793,7 +4803,7 @@
       </c>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="25">
         <v>1030220</v>
       </c>
@@ -4813,7 +4823,7 @@
       </c>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="25">
         <v>1030230</v>
       </c>
@@ -4833,7 +4843,7 @@
       </c>
       <c r="H59" s="3"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="25">
         <v>1030240</v>
       </c>
@@ -4853,7 +4863,7 @@
       </c>
       <c r="H60" s="3"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="25">
         <v>1030250</v>
       </c>
@@ -4873,7 +4883,7 @@
       </c>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="25">
         <v>1030260</v>
       </c>
@@ -4891,7 +4901,7 @@
       </c>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="25">
         <v>1030270</v>
       </c>
@@ -4909,7 +4919,7 @@
       </c>
       <c r="H63" s="3"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="25">
         <v>1030280</v>
       </c>
@@ -4927,7 +4937,7 @@
       </c>
       <c r="H64" s="3"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="25">
         <v>1030290</v>
       </c>
@@ -4947,7 +4957,7 @@
         <v>10204</v>
       </c>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="25">
         <v>1030300</v>
       </c>
@@ -4967,7 +4977,7 @@
       </c>
       <c r="H66" s="3"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="25">
         <v>1030310</v>
       </c>
@@ -4987,7 +4997,7 @@
       </c>
       <c r="H67" s="3"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="25">
         <v>1030320</v>
       </c>
@@ -5007,7 +5017,7 @@
       </c>
       <c r="H68" s="3"/>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="25">
         <v>1030330</v>
       </c>
@@ -5027,7 +5037,7 @@
         <v>10208</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="25">
         <v>1030340</v>
       </c>
@@ -5047,7 +5057,7 @@
       </c>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="25">
         <v>1030350</v>
       </c>
@@ -5067,7 +5077,7 @@
       </c>
       <c r="H71" s="3"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="25">
         <v>1030360</v>
       </c>
@@ -5085,7 +5095,7 @@
       </c>
       <c r="H72" s="3"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="25">
         <v>1030370</v>
       </c>
@@ -5103,7 +5113,7 @@
       </c>
       <c r="H73" s="3"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="25">
         <v>1030380</v>
       </c>
@@ -5121,7 +5131,7 @@
       </c>
       <c r="H74" s="3"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="25">
         <v>1030390</v>
       </c>
@@ -5139,7 +5149,7 @@
       </c>
       <c r="H75" s="3"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="25">
         <v>1030400</v>
       </c>
@@ -5159,7 +5169,7 @@
       </c>
       <c r="H76" s="3"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="25">
         <v>1030410</v>
       </c>
@@ -5179,7 +5189,7 @@
       </c>
       <c r="H77" s="3"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="25">
         <v>1030420</v>
       </c>
@@ -5197,7 +5207,7 @@
       </c>
       <c r="H78" s="3"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="25">
         <v>1030430</v>
       </c>
@@ -5215,7 +5225,7 @@
       </c>
       <c r="H79" s="3"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="25">
         <v>1030440</v>
       </c>
@@ -5233,7 +5243,7 @@
       </c>
       <c r="H80" s="3"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="25">
         <v>1030450</v>
       </c>
@@ -5251,7 +5261,7 @@
       </c>
       <c r="H81" s="3"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="25">
         <v>1030460</v>
       </c>
@@ -5271,7 +5281,7 @@
       </c>
       <c r="H82" s="3"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="25">
         <v>1030470</v>
       </c>
@@ -5291,7 +5301,7 @@
       </c>
       <c r="H83" s="3"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="25">
         <v>1030480</v>
       </c>
@@ -5311,7 +5321,7 @@
       </c>
       <c r="H84" s="3"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="25">
         <v>1030490</v>
       </c>
@@ -5329,7 +5339,7 @@
       </c>
       <c r="H85" s="3"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="25">
         <v>1030500</v>
       </c>
@@ -5349,7 +5359,7 @@
       </c>
       <c r="H86" s="3"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="25">
         <v>1030510</v>
       </c>
@@ -5367,7 +5377,7 @@
       </c>
       <c r="H87" s="3"/>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="25">
         <v>1030520</v>
       </c>
@@ -5385,7 +5395,7 @@
       </c>
       <c r="H88" s="3"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="25">
         <v>1030530</v>
       </c>
@@ -5403,7 +5413,7 @@
       </c>
       <c r="H89" s="3"/>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="25">
         <v>1030540</v>
       </c>
@@ -5421,7 +5431,7 @@
       </c>
       <c r="H90" s="3"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="25">
         <v>1030550</v>
       </c>
@@ -5439,7 +5449,7 @@
       </c>
       <c r="H91" s="3"/>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="25">
         <v>1030560</v>
       </c>
@@ -5457,7 +5467,7 @@
       </c>
       <c r="H92" s="3"/>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="25">
         <v>1030570</v>
       </c>
@@ -5475,7 +5485,7 @@
       </c>
       <c r="H93" s="3"/>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="25">
         <v>1030580</v>
       </c>
@@ -5493,7 +5503,7 @@
       </c>
       <c r="H94" s="3"/>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="25">
         <v>1030590</v>
       </c>
@@ -5513,7 +5523,7 @@
       </c>
       <c r="H95" s="3"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="25">
         <v>1030600</v>
       </c>
@@ -5533,7 +5543,7 @@
         <v>10205</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="25">
         <v>1030610</v>
       </c>
@@ -5542,8 +5552,8 @@
       </c>
       <c r="C97" s="3"/>
       <c r="D97" s="3"/>
-      <c r="E97" s="3" t="s">
-        <v>229</v>
+      <c r="E97" s="57" t="s">
+        <v>604</v>
       </c>
       <c r="F97" s="3"/>
       <c r="G97" s="25">
@@ -5551,7 +5561,7 @@
       </c>
       <c r="H97" s="3"/>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="25">
         <v>1030620</v>
       </c>
@@ -5571,7 +5581,7 @@
       </c>
       <c r="H98" s="3"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="25">
         <v>1030630</v>
       </c>
@@ -5591,7 +5601,7 @@
       </c>
       <c r="H99" s="3"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="25">
         <v>1030640</v>
       </c>
@@ -5609,7 +5619,7 @@
       </c>
       <c r="H100" s="3"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="25">
         <v>1030650</v>
       </c>
@@ -5627,7 +5637,7 @@
       </c>
       <c r="H101" s="3"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="25">
         <v>1030660</v>
       </c>
@@ -5647,7 +5657,7 @@
       </c>
       <c r="H102" s="3"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="25">
         <v>1030670</v>
       </c>
@@ -5667,7 +5677,7 @@
       </c>
       <c r="H103" s="3"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="25">
         <v>1030680</v>
       </c>
@@ -5687,7 +5697,7 @@
       </c>
       <c r="H104" s="3"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="25">
         <v>1030690</v>
       </c>
@@ -5705,7 +5715,7 @@
       </c>
       <c r="H105" s="3"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="25">
         <v>1030700</v>
       </c>
@@ -5725,7 +5735,7 @@
       </c>
       <c r="H106" s="3"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="25">
         <v>1030710</v>
       </c>
@@ -5745,7 +5755,7 @@
       </c>
       <c r="H107" s="3"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="25">
         <v>1030720</v>
       </c>
@@ -5765,7 +5775,7 @@
       </c>
       <c r="H108" s="3"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="25">
         <v>1030730</v>
       </c>
@@ -5785,7 +5795,7 @@
       </c>
       <c r="H109" s="3"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="25">
         <v>1030740</v>
       </c>
@@ -5805,7 +5815,7 @@
       </c>
       <c r="H110" s="3"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="25">
         <v>1030750</v>
       </c>
@@ -5825,7 +5835,7 @@
       </c>
       <c r="H111" s="3"/>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="25">
         <v>1030760</v>
       </c>
@@ -5845,7 +5855,7 @@
       </c>
       <c r="H112" s="3"/>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="25">
         <v>1030770</v>
       </c>
@@ -5865,7 +5875,7 @@
       </c>
       <c r="H113" s="3"/>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="25">
         <v>1030780</v>
       </c>
@@ -5885,7 +5895,7 @@
       </c>
       <c r="H114" s="3"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="25">
         <v>1030790</v>
       </c>
@@ -5905,7 +5915,7 @@
       </c>
       <c r="H115" s="3"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="25">
         <v>1030800</v>
       </c>
@@ -5925,7 +5935,7 @@
       </c>
       <c r="H116" s="3"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="25">
         <v>1030810</v>
       </c>
@@ -5945,7 +5955,7 @@
       </c>
       <c r="H117" s="3"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="25">
         <v>1030820</v>
       </c>
@@ -5965,7 +5975,7 @@
       </c>
       <c r="H118" s="3"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="25">
         <v>1030830</v>
       </c>
@@ -5985,7 +5995,7 @@
       </c>
       <c r="H119" s="3"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" s="25">
         <v>1030840</v>
       </c>
@@ -6005,7 +6015,7 @@
       </c>
       <c r="H120" s="3"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" s="25">
         <v>1030850</v>
       </c>
@@ -6025,7 +6035,7 @@
       </c>
       <c r="H121" s="3"/>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" s="25">
         <v>1030860</v>
       </c>
@@ -6045,7 +6055,7 @@
       </c>
       <c r="H122" s="3"/>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" s="25">
         <v>1030870</v>
       </c>
@@ -6065,7 +6075,7 @@
       </c>
       <c r="H123" s="3"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" s="25">
         <v>1030880</v>
       </c>
@@ -6085,7 +6095,7 @@
       </c>
       <c r="H124" s="3"/>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" s="25">
         <v>1030890</v>
       </c>
@@ -6105,7 +6115,7 @@
       </c>
       <c r="H125" s="3"/>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" s="25">
         <v>1030900</v>
       </c>
@@ -6125,7 +6135,7 @@
       </c>
       <c r="H126" s="3"/>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" s="25">
         <v>1030910</v>
       </c>
@@ -6145,7 +6155,7 @@
       </c>
       <c r="H127" s="3"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" s="25">
         <v>1030920</v>
       </c>
@@ -6165,7 +6175,7 @@
       </c>
       <c r="H128" s="3"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" s="25">
         <v>1030930</v>
       </c>
@@ -6185,7 +6195,7 @@
       </c>
       <c r="H129" s="3"/>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" s="25">
         <v>1030940</v>
       </c>
@@ -6205,7 +6215,7 @@
       </c>
       <c r="H130" s="3"/>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" s="25">
         <v>1030950</v>
       </c>
@@ -6223,7 +6233,7 @@
       </c>
       <c r="H131" s="3"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" s="25">
         <v>1030960</v>
       </c>
@@ -6243,7 +6253,7 @@
       </c>
       <c r="H132" s="3"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" s="25">
         <v>1030970</v>
       </c>
@@ -6263,7 +6273,7 @@
       </c>
       <c r="H133" s="3"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" s="25">
         <v>1030980</v>
       </c>
@@ -6283,7 +6293,7 @@
       </c>
       <c r="H134" s="3"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" s="25">
         <v>1030990</v>
       </c>
@@ -6303,7 +6313,7 @@
       </c>
       <c r="H135" s="3"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" s="25">
         <v>1031000</v>
       </c>
@@ -6323,7 +6333,7 @@
       </c>
       <c r="H136" s="3"/>
     </row>
-    <row r="137" spans="1:8">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" s="25">
         <v>1031010</v>
       </c>
@@ -6343,7 +6353,7 @@
       </c>
       <c r="H137" s="3"/>
     </row>
-    <row r="138" spans="1:8">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" s="25">
         <v>1031020</v>
       </c>
@@ -6361,7 +6371,7 @@
       </c>
       <c r="H138" s="3"/>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" s="25">
         <v>1031030</v>
       </c>
@@ -6381,7 +6391,7 @@
       </c>
       <c r="H139" s="3"/>
     </row>
-    <row r="140" spans="1:8">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" s="25">
         <v>1031040</v>
       </c>
@@ -6401,7 +6411,7 @@
       </c>
       <c r="H140" s="3"/>
     </row>
-    <row r="141" spans="1:8">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" s="25">
         <v>1031050</v>
       </c>
@@ -6421,7 +6431,7 @@
       </c>
       <c r="H141" s="3"/>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" s="25">
         <v>1031060</v>
       </c>
@@ -6441,7 +6451,7 @@
       </c>
       <c r="H142" s="3"/>
     </row>
-    <row r="143" spans="1:8">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" s="25">
         <v>1031070</v>
       </c>
@@ -6461,7 +6471,7 @@
       </c>
       <c r="H143" s="3"/>
     </row>
-    <row r="144" spans="1:8">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" s="25">
         <v>1031080</v>
       </c>
@@ -6481,7 +6491,7 @@
       </c>
       <c r="H144" s="3"/>
     </row>
-    <row r="145" spans="1:8">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" s="25">
         <v>1031090</v>
       </c>
@@ -6499,7 +6509,7 @@
       </c>
       <c r="H145" s="3"/>
     </row>
-    <row r="146" spans="1:8">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" s="25">
         <v>1031100</v>
       </c>
@@ -6519,7 +6529,7 @@
       </c>
       <c r="H146" s="3"/>
     </row>
-    <row r="147" spans="1:8">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" s="25">
         <v>1031110</v>
       </c>
@@ -6539,7 +6549,7 @@
       </c>
       <c r="H147" s="3"/>
     </row>
-    <row r="148" spans="1:8">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" s="25">
         <v>1031120</v>
       </c>
@@ -6559,7 +6569,7 @@
       </c>
       <c r="H148" s="3"/>
     </row>
-    <row r="149" spans="1:8">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" s="25">
         <v>1031130</v>
       </c>
@@ -6579,7 +6589,7 @@
       </c>
       <c r="H149" s="3"/>
     </row>
-    <row r="150" spans="1:8">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" s="25">
         <v>1031140</v>
       </c>
@@ -6599,7 +6609,7 @@
       </c>
       <c r="H150" s="3"/>
     </row>
-    <row r="151" spans="1:8">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" s="25">
         <v>1031150</v>
       </c>
@@ -6617,7 +6627,7 @@
       </c>
       <c r="H151" s="3"/>
     </row>
-    <row r="152" spans="1:8">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" s="25">
         <v>1031160</v>
       </c>
@@ -6637,7 +6647,7 @@
       </c>
       <c r="H152" s="3"/>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" s="25">
         <v>1031170</v>
       </c>
@@ -6657,7 +6667,7 @@
       </c>
       <c r="H153" s="3"/>
     </row>
-    <row r="154" spans="1:8">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" s="25">
         <v>1031180</v>
       </c>
@@ -6675,7 +6685,7 @@
       </c>
       <c r="H154" s="3"/>
     </row>
-    <row r="155" spans="1:8">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" s="25">
         <v>1031190</v>
       </c>
@@ -6693,7 +6703,7 @@
         <v>10206</v>
       </c>
     </row>
-    <row r="156" spans="1:8">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" s="25">
         <v>1031200</v>
       </c>
@@ -6702,8 +6712,8 @@
       </c>
       <c r="C156" s="3"/>
       <c r="D156" s="3"/>
-      <c r="E156" s="3" t="s">
-        <v>289</v>
+      <c r="E156" s="57" t="s">
+        <v>605</v>
       </c>
       <c r="F156" s="3"/>
       <c r="G156" s="25">
@@ -6711,7 +6721,7 @@
       </c>
       <c r="H156" s="3"/>
     </row>
-    <row r="157" spans="1:8">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" s="25">
         <v>1031210</v>
       </c>
@@ -6721,7 +6731,7 @@
       <c r="C157" s="3"/>
       <c r="D157" s="3"/>
       <c r="E157" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F157" s="3"/>
       <c r="G157" s="25">
@@ -6729,7 +6739,7 @@
       </c>
       <c r="H157" s="3"/>
     </row>
-    <row r="158" spans="1:8">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" s="25">
         <v>1031220</v>
       </c>
@@ -6741,7 +6751,7 @@
       </c>
       <c r="D158" s="3"/>
       <c r="E158" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="F158" s="3"/>
       <c r="G158" s="25">
@@ -6749,7 +6759,7 @@
       </c>
       <c r="H158" s="3"/>
     </row>
-    <row r="159" spans="1:8">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" s="25">
         <v>1031230</v>
       </c>
@@ -6761,7 +6771,7 @@
       </c>
       <c r="D159" s="3"/>
       <c r="E159" s="3" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F159" s="3"/>
       <c r="G159" s="25">
@@ -6769,7 +6779,7 @@
       </c>
       <c r="H159" s="3"/>
     </row>
-    <row r="160" spans="1:8">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" s="25">
         <v>1031240</v>
       </c>
@@ -6779,7 +6789,7 @@
       <c r="C160" s="3"/>
       <c r="D160" s="3"/>
       <c r="E160" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F160" s="3"/>
       <c r="G160" s="25">
@@ -6787,7 +6797,7 @@
       </c>
       <c r="H160" s="3"/>
     </row>
-    <row r="161" spans="1:8">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" s="25">
         <v>1031250</v>
       </c>
@@ -6797,7 +6807,7 @@
       <c r="C161" s="3"/>
       <c r="D161" s="3"/>
       <c r="E161" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="F161" s="3"/>
       <c r="G161" s="25">
@@ -6805,7 +6815,7 @@
       </c>
       <c r="H161" s="3"/>
     </row>
-    <row r="162" spans="1:8">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" s="25">
         <v>1031260</v>
       </c>
@@ -6817,7 +6827,7 @@
       </c>
       <c r="D162" s="3"/>
       <c r="E162" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F162" s="3"/>
       <c r="G162" s="25">
@@ -6825,7 +6835,7 @@
       </c>
       <c r="H162" s="3"/>
     </row>
-    <row r="163" spans="1:8">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" s="25">
         <v>1031270</v>
       </c>
@@ -6837,7 +6847,7 @@
       </c>
       <c r="D163" s="3"/>
       <c r="E163" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F163" s="3"/>
       <c r="G163" s="25">
@@ -6845,7 +6855,7 @@
       </c>
       <c r="H163" s="3"/>
     </row>
-    <row r="164" spans="1:8">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" s="25">
         <v>1031280</v>
       </c>
@@ -6857,7 +6867,7 @@
       </c>
       <c r="D164" s="3"/>
       <c r="E164" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F164" s="3"/>
       <c r="G164" s="25">
@@ -6865,7 +6875,7 @@
       </c>
       <c r="H164" s="3"/>
     </row>
-    <row r="165" spans="1:8">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" s="25">
         <v>1031290</v>
       </c>
@@ -6877,7 +6887,7 @@
       </c>
       <c r="D165" s="3"/>
       <c r="E165" s="3" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F165" s="3"/>
       <c r="G165" s="25">
@@ -6885,7 +6895,7 @@
       </c>
       <c r="H165" s="3"/>
     </row>
-    <row r="166" spans="1:8">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" s="25">
         <v>1031300</v>
       </c>
@@ -6897,7 +6907,7 @@
       </c>
       <c r="D166" s="3"/>
       <c r="E166" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F166" s="3"/>
       <c r="G166" s="25">
@@ -6905,7 +6915,7 @@
       </c>
       <c r="H166" s="3"/>
     </row>
-    <row r="167" spans="1:8">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" s="25">
         <v>1031310</v>
       </c>
@@ -6917,7 +6927,7 @@
       </c>
       <c r="D167" s="3"/>
       <c r="E167" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="F167" s="3"/>
       <c r="G167" s="25">
@@ -6925,7 +6935,7 @@
       </c>
       <c r="H167" s="3"/>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" s="25">
         <v>1031320</v>
       </c>
@@ -6937,7 +6947,7 @@
       </c>
       <c r="D168" s="3"/>
       <c r="E168" s="3" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="F168" s="3"/>
       <c r="G168" s="25">
@@ -6945,7 +6955,7 @@
       </c>
       <c r="H168" s="3"/>
     </row>
-    <row r="169" spans="1:8">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" s="25">
         <v>1031330</v>
       </c>
@@ -6955,7 +6965,7 @@
       <c r="C169" s="3"/>
       <c r="D169" s="3"/>
       <c r="E169" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F169" s="3"/>
       <c r="G169" s="25">
@@ -6963,7 +6973,7 @@
       </c>
       <c r="H169" s="3"/>
     </row>
-    <row r="170" spans="1:8">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" s="25">
         <v>1031340</v>
       </c>
@@ -6973,7 +6983,7 @@
       <c r="C170" s="3"/>
       <c r="D170" s="3"/>
       <c r="E170" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F170" s="3"/>
       <c r="G170" s="25">
@@ -6981,7 +6991,7 @@
       </c>
       <c r="H170" s="3"/>
     </row>
-    <row r="171" spans="1:8">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" s="25">
         <v>1031350</v>
       </c>
@@ -6989,11 +6999,11 @@
         <v>0</v>
       </c>
       <c r="C171" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D171" s="3"/>
       <c r="E171" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F171" s="3"/>
       <c r="G171" s="25">
@@ -7001,7 +7011,7 @@
       </c>
       <c r="H171" s="3"/>
     </row>
-    <row r="172" spans="1:8">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" s="25">
         <v>1031360</v>
       </c>
@@ -7009,11 +7019,11 @@
         <v>0</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D172" s="3"/>
       <c r="E172" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F172" s="3"/>
       <c r="G172" s="25">
@@ -7021,7 +7031,7 @@
       </c>
       <c r="H172" s="3"/>
     </row>
-    <row r="173" spans="1:8">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" s="25">
         <v>1031370</v>
       </c>
@@ -7029,11 +7039,11 @@
         <v>0</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D173" s="3"/>
       <c r="E173" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F173" s="3"/>
       <c r="G173" s="25">
@@ -7041,7 +7051,7 @@
       </c>
       <c r="H173" s="3"/>
     </row>
-    <row r="174" spans="1:8">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" s="25">
         <v>1031380</v>
       </c>
@@ -7049,11 +7059,11 @@
         <v>0</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D174" s="3"/>
       <c r="E174" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F174" s="3"/>
       <c r="G174" s="25">
@@ -7061,7 +7071,7 @@
       </c>
       <c r="H174" s="3"/>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" s="25">
         <v>1031390</v>
       </c>
@@ -7069,11 +7079,11 @@
         <v>0</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D175" s="3"/>
       <c r="E175" s="3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F175" s="3"/>
       <c r="G175" s="25">
@@ -7081,7 +7091,7 @@
       </c>
       <c r="H175" s="3"/>
     </row>
-    <row r="176" spans="1:8">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" s="25">
         <v>1031400</v>
       </c>
@@ -7089,11 +7099,11 @@
         <v>0</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D176" s="3"/>
       <c r="E176" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F176" s="3"/>
       <c r="G176" s="25">
@@ -7101,7 +7111,7 @@
       </c>
       <c r="H176" s="3"/>
     </row>
-    <row r="177" spans="1:8">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" s="25">
         <v>1031410</v>
       </c>
@@ -7109,11 +7119,11 @@
         <v>0</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D177" s="3"/>
       <c r="E177" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F177" s="3"/>
       <c r="G177" s="25">
@@ -7121,7 +7131,7 @@
       </c>
       <c r="H177" s="3"/>
     </row>
-    <row r="178" spans="1:8">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" s="25">
         <v>1031420</v>
       </c>
@@ -7129,11 +7139,11 @@
         <v>0</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D178" s="3"/>
       <c r="E178" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="F178" s="3"/>
       <c r="G178" s="25">
@@ -7141,7 +7151,7 @@
       </c>
       <c r="H178" s="3"/>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" s="25">
         <v>1031430</v>
       </c>
@@ -7149,11 +7159,11 @@
         <v>0</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D179" s="3"/>
       <c r="E179" s="3" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F179" s="3"/>
       <c r="G179" s="25">
@@ -7161,7 +7171,7 @@
       </c>
       <c r="H179" s="3"/>
     </row>
-    <row r="180" spans="1:8">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" s="25">
         <v>1031440</v>
       </c>
@@ -7171,7 +7181,7 @@
       <c r="C180" s="3"/>
       <c r="D180" s="3"/>
       <c r="E180" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F180" s="3"/>
       <c r="G180" s="25">
@@ -7179,7 +7189,7 @@
       </c>
       <c r="H180" s="3"/>
     </row>
-    <row r="181" spans="1:8">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" s="25">
         <v>1031450</v>
       </c>
@@ -7187,11 +7197,11 @@
         <v>0</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D181" s="3"/>
       <c r="E181" s="3" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F181" s="3"/>
       <c r="G181" s="25">
@@ -7199,7 +7209,7 @@
       </c>
       <c r="H181" s="3"/>
     </row>
-    <row r="182" spans="1:8">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" s="25">
         <v>1031460</v>
       </c>
@@ -7207,11 +7217,11 @@
         <v>0</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D182" s="3"/>
       <c r="E182" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F182" s="3"/>
       <c r="G182" s="25">
@@ -7219,7 +7229,7 @@
       </c>
       <c r="H182" s="3"/>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" s="25">
         <v>1031470</v>
       </c>
@@ -7229,7 +7239,7 @@
       <c r="C183" s="3"/>
       <c r="D183" s="3"/>
       <c r="E183" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F183" s="3"/>
       <c r="G183" s="25">
@@ -7237,7 +7247,7 @@
       </c>
       <c r="H183" s="3"/>
     </row>
-    <row r="184" spans="1:8">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" s="25">
         <v>1031480</v>
       </c>
@@ -7245,11 +7255,11 @@
         <v>0</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D184" s="3"/>
       <c r="E184" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F184" s="3"/>
       <c r="G184" s="25">
@@ -7257,7 +7267,7 @@
       </c>
       <c r="H184" s="3"/>
     </row>
-    <row r="185" spans="1:8">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" s="25">
         <v>1031490</v>
       </c>
@@ -7265,11 +7275,11 @@
         <v>0</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D185" s="3"/>
       <c r="E185" s="3" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F185" s="3"/>
       <c r="G185" s="25">
@@ -7277,7 +7287,7 @@
       </c>
       <c r="H185" s="3"/>
     </row>
-    <row r="186" spans="1:8">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" s="25">
         <v>1031500</v>
       </c>
@@ -7285,11 +7295,11 @@
         <v>0</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D186" s="3"/>
       <c r="E186" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F186" s="3"/>
       <c r="G186" s="25">
@@ -7297,7 +7307,7 @@
       </c>
       <c r="H186" s="3"/>
     </row>
-    <row r="187" spans="1:8">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" s="25">
         <v>1031510</v>
       </c>
@@ -7305,11 +7315,11 @@
         <v>0</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D187" s="3"/>
       <c r="E187" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F187" s="3"/>
       <c r="G187" s="25">
@@ -7317,7 +7327,7 @@
       </c>
       <c r="H187" s="3"/>
     </row>
-    <row r="188" spans="1:8">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" s="25">
         <v>1031520</v>
       </c>
@@ -7327,7 +7337,7 @@
       <c r="C188" s="3"/>
       <c r="D188" s="3"/>
       <c r="E188" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="F188" s="3"/>
       <c r="G188" s="25">
@@ -7335,7 +7345,7 @@
       </c>
       <c r="H188" s="3"/>
     </row>
-    <row r="189" spans="1:8">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" s="25">
         <v>1031530</v>
       </c>
@@ -7347,7 +7357,7 @@
       </c>
       <c r="D189" s="3"/>
       <c r="E189" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="F189" s="3"/>
       <c r="G189" s="25">
@@ -7355,7 +7365,7 @@
       </c>
       <c r="H189" s="3"/>
     </row>
-    <row r="190" spans="1:8">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" s="25">
         <v>1031540</v>
       </c>
@@ -7367,7 +7377,7 @@
       </c>
       <c r="D190" s="3"/>
       <c r="E190" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="F190" s="3"/>
       <c r="G190" s="25">
@@ -7375,7 +7385,7 @@
       </c>
       <c r="H190" s="3"/>
     </row>
-    <row r="191" spans="1:8">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" s="25">
         <v>1031550</v>
       </c>
@@ -7387,7 +7397,7 @@
       </c>
       <c r="D191" s="3"/>
       <c r="E191" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="F191" s="3"/>
       <c r="G191" s="25">
@@ -7395,7 +7405,7 @@
       </c>
       <c r="H191" s="3"/>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" s="25">
         <v>1031560</v>
       </c>
@@ -7407,7 +7417,7 @@
       </c>
       <c r="D192" s="3"/>
       <c r="E192" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="F192" s="3"/>
       <c r="G192" s="25">
@@ -7415,7 +7425,7 @@
       </c>
       <c r="H192" s="3"/>
     </row>
-    <row r="193" spans="1:8">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" s="25">
         <v>1031570</v>
       </c>
@@ -7423,11 +7433,11 @@
         <v>0</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D193" s="3"/>
       <c r="E193" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="F193" s="3"/>
       <c r="G193" s="25">
@@ -7435,7 +7445,7 @@
       </c>
       <c r="H193" s="3"/>
     </row>
-    <row r="194" spans="1:8">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" s="25">
         <v>1031580</v>
       </c>
@@ -7443,11 +7453,11 @@
         <v>0</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D194" s="3"/>
       <c r="E194" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="F194" s="3"/>
       <c r="G194" s="25">
@@ -7455,7 +7465,7 @@
       </c>
       <c r="H194" s="3"/>
     </row>
-    <row r="195" spans="1:8">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" s="25">
         <v>1031590</v>
       </c>
@@ -7463,11 +7473,11 @@
         <v>0</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D195" s="3"/>
       <c r="E195" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="F195" s="3"/>
       <c r="G195" s="25">
@@ -7475,7 +7485,7 @@
       </c>
       <c r="H195" s="3"/>
     </row>
-    <row r="196" spans="1:8">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" s="25">
         <v>1031600</v>
       </c>
@@ -7487,7 +7497,7 @@
       </c>
       <c r="D196" s="3"/>
       <c r="E196" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="F196" s="3"/>
       <c r="G196" s="25">
@@ -7495,7 +7505,7 @@
       </c>
       <c r="H196" s="3"/>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" s="25">
         <v>1031610</v>
       </c>
@@ -7507,7 +7517,7 @@
       </c>
       <c r="D197" s="3"/>
       <c r="E197" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="F197" s="3"/>
       <c r="G197" s="25">
@@ -7515,7 +7525,7 @@
       </c>
       <c r="H197" s="3"/>
     </row>
-    <row r="198" spans="1:8">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" s="25">
         <v>1031620</v>
       </c>
@@ -7523,11 +7533,11 @@
         <v>0</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D198" s="3"/>
       <c r="E198" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F198" s="3"/>
       <c r="G198" s="25">
@@ -7535,7 +7545,7 @@
       </c>
       <c r="H198" s="3"/>
     </row>
-    <row r="199" spans="1:8">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" s="25">
         <v>1031630</v>
       </c>
@@ -7543,11 +7553,11 @@
         <v>0</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D199" s="3"/>
       <c r="E199" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="F199" s="3"/>
       <c r="G199" s="25">
@@ -7555,7 +7565,7 @@
       </c>
       <c r="H199" s="3"/>
     </row>
-    <row r="200" spans="1:8">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" s="25">
         <v>1031640</v>
       </c>
@@ -7563,11 +7573,11 @@
         <v>0</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D200" s="3"/>
       <c r="E200" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F200" s="3"/>
       <c r="G200" s="25">
@@ -7575,7 +7585,7 @@
       </c>
       <c r="H200" s="3"/>
     </row>
-    <row r="201" spans="1:8">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" s="25">
         <v>1031650</v>
       </c>
@@ -7583,11 +7593,11 @@
         <v>0</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D201" s="3"/>
       <c r="E201" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F201" s="3"/>
       <c r="G201" s="25">
@@ -7595,7 +7605,7 @@
       </c>
       <c r="H201" s="3"/>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" s="25">
         <v>1031660</v>
       </c>
@@ -7603,11 +7613,11 @@
         <v>0</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D202" s="3"/>
       <c r="E202" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F202" s="3"/>
       <c r="G202" s="25">
@@ -7615,7 +7625,7 @@
       </c>
       <c r="H202" s="3"/>
     </row>
-    <row r="203" spans="1:8">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" s="25">
         <v>1031670</v>
       </c>
@@ -7623,11 +7633,11 @@
         <v>0</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D203" s="3"/>
       <c r="E203" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="F203" s="3"/>
       <c r="G203" s="25">
@@ -7635,7 +7645,7 @@
       </c>
       <c r="H203" s="3"/>
     </row>
-    <row r="204" spans="1:8">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" s="25">
         <v>1031680</v>
       </c>
@@ -7643,11 +7653,11 @@
         <v>0</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D204" s="3"/>
       <c r="E204" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="F204" s="3"/>
       <c r="G204" s="25">
@@ -7655,7 +7665,7 @@
       </c>
       <c r="H204" s="3"/>
     </row>
-    <row r="205" spans="1:8">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" s="25">
         <v>1031690</v>
       </c>
@@ -7663,11 +7673,11 @@
         <v>0</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D205" s="3"/>
       <c r="E205" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="F205" s="3"/>
       <c r="G205" s="25">
@@ -7675,7 +7685,7 @@
       </c>
       <c r="H205" s="3"/>
     </row>
-    <row r="206" spans="1:8">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" s="25">
         <v>1031700</v>
       </c>
@@ -7687,7 +7697,7 @@
       </c>
       <c r="D206" s="3"/>
       <c r="E206" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F206" s="3"/>
       <c r="G206" s="25">
@@ -7695,7 +7705,7 @@
       </c>
       <c r="H206" s="3"/>
     </row>
-    <row r="207" spans="1:8">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" s="25">
         <v>1031710</v>
       </c>
@@ -7705,7 +7715,7 @@
       <c r="C207" s="3"/>
       <c r="D207" s="3"/>
       <c r="E207" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F207" s="3"/>
       <c r="G207" s="25">
@@ -7713,7 +7723,7 @@
       </c>
       <c r="H207" s="3"/>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" s="25">
         <v>1031720</v>
       </c>
@@ -7721,11 +7731,11 @@
         <v>0</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D208" s="3"/>
       <c r="E208" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="F208" s="3"/>
       <c r="G208" s="25">
@@ -7733,7 +7743,7 @@
       </c>
       <c r="H208" s="3"/>
     </row>
-    <row r="209" spans="1:8">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" s="25">
         <v>1031730</v>
       </c>
@@ -7743,7 +7753,7 @@
       <c r="C209" s="3"/>
       <c r="D209" s="3"/>
       <c r="E209" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F209" s="3"/>
       <c r="G209" s="25">
@@ -7751,7 +7761,7 @@
       </c>
       <c r="H209" s="3"/>
     </row>
-    <row r="210" spans="1:8">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" s="25">
         <v>1031740</v>
       </c>
@@ -7763,7 +7773,7 @@
       </c>
       <c r="D210" s="3"/>
       <c r="E210" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F210" s="3"/>
       <c r="G210" s="25">
@@ -7771,7 +7781,7 @@
       </c>
       <c r="H210" s="3"/>
     </row>
-    <row r="211" spans="1:8">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" s="25">
         <v>1031750</v>
       </c>
@@ -7779,11 +7789,11 @@
         <v>0</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D211" s="3"/>
       <c r="E211" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="F211" s="3"/>
       <c r="G211" s="25">
@@ -7791,7 +7801,7 @@
       </c>
       <c r="H211" s="3"/>
     </row>
-    <row r="212" spans="1:8">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" s="25">
         <v>1031760</v>
       </c>
@@ -7803,7 +7813,7 @@
       </c>
       <c r="D212" s="3"/>
       <c r="E212" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="F212" s="3"/>
       <c r="G212" s="25">
@@ -7811,7 +7821,7 @@
       </c>
       <c r="H212" s="3"/>
     </row>
-    <row r="213" spans="1:8">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" s="25">
         <v>1031770</v>
       </c>
@@ -7823,7 +7833,7 @@
       </c>
       <c r="D213" s="3"/>
       <c r="E213" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F213" s="3"/>
       <c r="G213" s="25">
@@ -7831,7 +7841,7 @@
       </c>
       <c r="H213" s="3"/>
     </row>
-    <row r="214" spans="1:8">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" s="25">
         <v>1031780</v>
       </c>
@@ -7843,7 +7853,7 @@
       </c>
       <c r="D214" s="3"/>
       <c r="E214" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="F214" s="3"/>
       <c r="G214" s="25">
@@ -7851,7 +7861,7 @@
       </c>
       <c r="H214" s="3"/>
     </row>
-    <row r="215" spans="1:8">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" s="25">
         <v>1031790</v>
       </c>
@@ -7863,7 +7873,7 @@
       </c>
       <c r="D215" s="3"/>
       <c r="E215" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F215" s="3"/>
       <c r="G215" s="25">
@@ -7871,7 +7881,7 @@
       </c>
       <c r="H215" s="3"/>
     </row>
-    <row r="216" spans="1:8">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" s="25">
         <v>1031800</v>
       </c>
@@ -7883,7 +7893,7 @@
       </c>
       <c r="D216" s="3"/>
       <c r="E216" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F216" s="3"/>
       <c r="G216" s="25">
@@ -7891,7 +7901,7 @@
       </c>
       <c r="H216" s="3"/>
     </row>
-    <row r="217" spans="1:8">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" s="25">
         <v>1031810</v>
       </c>
@@ -7901,7 +7911,7 @@
       <c r="C217" s="3"/>
       <c r="D217" s="3"/>
       <c r="E217" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="F217" s="3"/>
       <c r="G217" s="25">
@@ -7909,7 +7919,7 @@
       </c>
       <c r="H217" s="3"/>
     </row>
-    <row r="218" spans="1:8">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" s="25">
         <v>1031820</v>
       </c>
@@ -7919,7 +7929,7 @@
       <c r="C218" s="3"/>
       <c r="D218" s="3"/>
       <c r="E218" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="F218" s="3"/>
       <c r="G218" s="25">
@@ -7927,7 +7937,7 @@
       </c>
       <c r="H218" s="3"/>
     </row>
-    <row r="219" spans="1:8">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" s="25">
         <v>1031830</v>
       </c>
@@ -7935,11 +7945,11 @@
         <v>0</v>
       </c>
       <c r="C219" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D219" s="3"/>
       <c r="E219" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F219" s="3"/>
       <c r="G219" s="25">
@@ -7947,7 +7957,7 @@
       </c>
       <c r="H219" s="3"/>
     </row>
-    <row r="220" spans="1:8">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" s="25">
         <v>1031840</v>
       </c>
@@ -7955,11 +7965,11 @@
         <v>0</v>
       </c>
       <c r="C220" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D220" s="3"/>
       <c r="E220" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F220" s="3"/>
       <c r="G220" s="25">
@@ -7967,7 +7977,7 @@
       </c>
       <c r="H220" s="3"/>
     </row>
-    <row r="221" spans="1:8">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" s="25">
         <v>1031850</v>
       </c>
@@ -7975,11 +7985,11 @@
         <v>0</v>
       </c>
       <c r="C221" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D221" s="3"/>
       <c r="E221" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F221" s="3"/>
       <c r="G221" s="25">
@@ -7987,7 +7997,7 @@
       </c>
       <c r="H221" s="3"/>
     </row>
-    <row r="222" spans="1:8">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" s="25">
         <v>1031860</v>
       </c>
@@ -7999,7 +8009,7 @@
       </c>
       <c r="D222" s="3"/>
       <c r="E222" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F222" s="3"/>
       <c r="G222" s="25">
@@ -8007,7 +8017,7 @@
       </c>
       <c r="H222" s="3"/>
     </row>
-    <row r="223" spans="1:8">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" s="25">
         <v>1031870</v>
       </c>
@@ -8019,7 +8029,7 @@
       </c>
       <c r="D223" s="3"/>
       <c r="E223" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F223" s="3"/>
       <c r="G223" s="25">
@@ -8027,7 +8037,7 @@
       </c>
       <c r="H223" s="3"/>
     </row>
-    <row r="224" spans="1:8">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" s="25">
         <v>1031880</v>
       </c>
@@ -8039,7 +8049,7 @@
       </c>
       <c r="D224" s="3"/>
       <c r="E224" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F224" s="3"/>
       <c r="G224" s="25">
@@ -8047,7 +8057,7 @@
       </c>
       <c r="H224" s="3"/>
     </row>
-    <row r="225" spans="1:8">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" s="25">
         <v>1031890</v>
       </c>
@@ -8059,7 +8069,7 @@
       </c>
       <c r="D225" s="3"/>
       <c r="E225" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F225" s="3"/>
       <c r="G225" s="25">
@@ -8067,7 +8077,7 @@
       </c>
       <c r="H225" s="3"/>
     </row>
-    <row r="226" spans="1:8">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" s="25">
         <v>1031900</v>
       </c>
@@ -8075,11 +8085,11 @@
         <v>0</v>
       </c>
       <c r="C226" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D226" s="3"/>
       <c r="E226" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F226" s="3"/>
       <c r="G226" s="25">
@@ -8087,7 +8097,7 @@
       </c>
       <c r="H226" s="3"/>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" s="25">
         <v>1031910</v>
       </c>
@@ -8095,11 +8105,11 @@
         <v>0</v>
       </c>
       <c r="C227" s="3" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D227" s="3"/>
       <c r="E227" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F227" s="3"/>
       <c r="G227" s="25">
@@ -8107,7 +8117,7 @@
       </c>
       <c r="H227" s="3"/>
     </row>
-    <row r="228" spans="1:8">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" s="25">
         <v>1031920</v>
       </c>
@@ -8115,11 +8125,11 @@
         <v>0</v>
       </c>
       <c r="C228" s="3" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="D228" s="3"/>
       <c r="E228" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F228" s="3"/>
       <c r="G228" s="25">
@@ -8127,7 +8137,7 @@
       </c>
       <c r="H228" s="3"/>
     </row>
-    <row r="229" spans="1:8">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" s="25">
         <v>1031930</v>
       </c>
@@ -8137,7 +8147,7 @@
       <c r="C229" s="3"/>
       <c r="D229" s="3"/>
       <c r="E229" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="F229" s="3"/>
       <c r="G229" s="25">
@@ -8145,7 +8155,7 @@
       </c>
       <c r="H229" s="3"/>
     </row>
-    <row r="230" spans="1:8">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" s="25">
         <v>1031940</v>
       </c>
@@ -8155,7 +8165,7 @@
       <c r="C230" s="3"/>
       <c r="D230" s="3"/>
       <c r="E230" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="F230" s="3"/>
       <c r="G230" s="25">
@@ -8163,7 +8173,7 @@
       </c>
       <c r="H230" s="3"/>
     </row>
-    <row r="231" spans="1:8">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" s="25">
         <v>1031950</v>
       </c>
@@ -8175,7 +8185,7 @@
       </c>
       <c r="D231" s="3"/>
       <c r="E231" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="F231" s="3"/>
       <c r="G231" s="25">
@@ -8183,7 +8193,7 @@
       </c>
       <c r="H231" s="3"/>
     </row>
-    <row r="232" spans="1:8">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" s="25">
         <v>1031960</v>
       </c>
@@ -8195,7 +8205,7 @@
       </c>
       <c r="D232" s="3"/>
       <c r="E232" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F232" s="3"/>
       <c r="G232" s="25">
@@ -8203,7 +8213,7 @@
       </c>
       <c r="H232" s="3"/>
     </row>
-    <row r="233" spans="1:8">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" s="25">
         <v>1031970</v>
       </c>
@@ -8215,7 +8225,7 @@
       </c>
       <c r="D233" s="3"/>
       <c r="E233" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F233" s="3"/>
       <c r="G233" s="25">
@@ -8223,7 +8233,7 @@
       </c>
       <c r="H233" s="3"/>
     </row>
-    <row r="234" spans="1:8">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" s="25">
         <v>1031980</v>
       </c>
@@ -8233,7 +8243,7 @@
       <c r="C234" s="25"/>
       <c r="D234" s="3"/>
       <c r="E234" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F234" s="3"/>
       <c r="G234" s="25">
@@ -8241,7 +8251,7 @@
       </c>
       <c r="H234" s="3"/>
     </row>
-    <row r="235" spans="1:8">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" s="25">
         <v>1031990</v>
       </c>
@@ -8253,7 +8263,7 @@
       </c>
       <c r="D235" s="3"/>
       <c r="E235" s="25" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="F235" s="3"/>
       <c r="G235" s="25">
@@ -8261,7 +8271,7 @@
       </c>
       <c r="H235" s="3"/>
     </row>
-    <row r="236" spans="1:8">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" s="25">
         <v>1032000</v>
       </c>
@@ -8271,7 +8281,7 @@
       <c r="C236" s="25"/>
       <c r="D236" s="3"/>
       <c r="E236" s="25" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="F236" s="3"/>
       <c r="G236" s="25">
@@ -8279,7 +8289,7 @@
       </c>
       <c r="H236" s="3"/>
     </row>
-    <row r="237" spans="1:8">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" s="25">
         <v>1032010</v>
       </c>
@@ -8289,7 +8299,7 @@
       <c r="C237" s="25"/>
       <c r="D237" s="3"/>
       <c r="E237" s="25" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="F237" s="3"/>
       <c r="G237" s="25">
@@ -8297,7 +8307,7 @@
       </c>
       <c r="H237" s="3"/>
     </row>
-    <row r="238" spans="1:8">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" s="25">
         <v>1032020</v>
       </c>
@@ -8309,7 +8319,7 @@
       </c>
       <c r="D238" s="3"/>
       <c r="E238" s="25" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="F238" s="3"/>
       <c r="G238" s="25">
@@ -8317,7 +8327,7 @@
       </c>
       <c r="H238" s="3"/>
     </row>
-    <row r="239" spans="1:8">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" s="25">
         <v>1032030</v>
       </c>
@@ -8329,7 +8339,7 @@
       </c>
       <c r="D239" s="3"/>
       <c r="E239" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="F239" s="3"/>
       <c r="G239" s="25">
@@ -8337,7 +8347,7 @@
       </c>
       <c r="H239" s="3"/>
     </row>
-    <row r="240" spans="1:8">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" s="25">
         <v>1032040</v>
       </c>
@@ -8347,7 +8357,7 @@
       <c r="C240" s="25"/>
       <c r="D240" s="3"/>
       <c r="E240" s="25" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="F240" s="3"/>
       <c r="G240" s="25">
@@ -8355,7 +8365,7 @@
       </c>
       <c r="H240" s="3"/>
     </row>
-    <row r="241" spans="1:8">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" s="25">
         <v>1032050</v>
       </c>
@@ -8365,7 +8375,7 @@
       <c r="C241" s="25"/>
       <c r="D241" s="3"/>
       <c r="E241" s="25" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="F241" s="3"/>
       <c r="G241" s="25">
@@ -8373,7 +8383,7 @@
       </c>
       <c r="H241" s="3"/>
     </row>
-    <row r="242" spans="1:8">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" s="25">
         <v>1032060</v>
       </c>
@@ -8381,11 +8391,11 @@
         <v>0</v>
       </c>
       <c r="C242" s="25" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D242" s="3"/>
       <c r="E242" s="25" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F242" s="3"/>
       <c r="G242" s="3"/>
@@ -8393,7 +8403,7 @@
         <v>10207</v>
       </c>
     </row>
-    <row r="243" spans="1:8">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" s="25">
         <v>1040010</v>
       </c>
@@ -8405,7 +8415,7 @@
       </c>
       <c r="D243" s="3"/>
       <c r="E243" s="25" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F243" s="3"/>
       <c r="G243" s="25">
@@ -8413,7 +8423,7 @@
       </c>
       <c r="H243" s="3"/>
     </row>
-    <row r="244" spans="1:8">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" s="25">
         <v>1040020</v>
       </c>
@@ -8425,7 +8435,7 @@
       </c>
       <c r="D244" s="3"/>
       <c r="E244" s="25" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F244" s="3"/>
       <c r="G244" s="25"/>
@@ -8433,7 +8443,7 @@
         <v>10209</v>
       </c>
     </row>
-    <row r="245" spans="1:8">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" s="25">
         <v>1040030</v>
       </c>
@@ -8443,7 +8453,7 @@
       <c r="C245" s="25"/>
       <c r="D245" s="3"/>
       <c r="E245" s="25" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F245" s="3"/>
       <c r="G245" s="25">
@@ -8451,7 +8461,7 @@
       </c>
       <c r="H245" s="3"/>
     </row>
-    <row r="246" spans="1:8">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" s="25">
         <v>1040040</v>
       </c>
@@ -8463,7 +8473,7 @@
       </c>
       <c r="D246" s="3"/>
       <c r="E246" s="25" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="F246" s="3"/>
       <c r="G246" s="25">
@@ -8471,7 +8481,7 @@
       </c>
       <c r="H246" s="3"/>
     </row>
-    <row r="247" spans="1:8">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" s="25">
         <v>1040050</v>
       </c>
@@ -8483,7 +8493,7 @@
       </c>
       <c r="D247" s="3"/>
       <c r="E247" s="25" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="F247" s="3"/>
       <c r="G247" s="25">
@@ -8491,7 +8501,7 @@
       </c>
       <c r="H247" s="3"/>
     </row>
-    <row r="248" spans="1:8">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" s="25">
         <v>1040060</v>
       </c>
@@ -8499,11 +8509,11 @@
         <v>0</v>
       </c>
       <c r="C248" s="25" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D248" s="3"/>
       <c r="E248" s="25" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="F248" s="3"/>
       <c r="G248" s="25">
@@ -8511,7 +8521,7 @@
       </c>
       <c r="H248" s="3"/>
     </row>
-    <row r="249" spans="1:8">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" s="25">
         <v>1040070</v>
       </c>
@@ -8521,7 +8531,7 @@
       <c r="C249" s="25"/>
       <c r="D249" s="3"/>
       <c r="E249" s="25" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F249" s="3"/>
       <c r="G249" s="25">
@@ -8529,7 +8539,7 @@
       </c>
       <c r="H249" s="3"/>
     </row>
-    <row r="250" spans="1:8">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" s="25">
         <v>1040080</v>
       </c>
@@ -8539,7 +8549,7 @@
       <c r="C250" s="25"/>
       <c r="D250" s="3"/>
       <c r="E250" s="25" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="F250" s="3"/>
       <c r="G250" s="25">
@@ -8547,7 +8557,7 @@
       </c>
       <c r="H250" s="3"/>
     </row>
-    <row r="251" spans="1:8">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" s="25">
         <v>1040090</v>
       </c>
@@ -8557,7 +8567,7 @@
       <c r="C251" s="25"/>
       <c r="D251" s="3"/>
       <c r="E251" s="25" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="F251" s="3"/>
       <c r="G251" s="25">
@@ -8565,7 +8575,7 @@
       </c>
       <c r="H251" s="3"/>
     </row>
-    <row r="252" spans="1:8">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" s="25">
         <v>1040100</v>
       </c>
@@ -8575,13 +8585,13 @@
       <c r="C252" s="25"/>
       <c r="D252" s="3"/>
       <c r="E252" s="25" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="F252" s="3"/>
       <c r="G252" s="25"/>
       <c r="H252" s="3"/>
     </row>
-    <row r="253" spans="1:8">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" s="25">
         <v>1040110</v>
       </c>
@@ -8591,7 +8601,7 @@
       <c r="C253" s="25"/>
       <c r="D253" s="3"/>
       <c r="E253" s="25" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="F253" s="3"/>
       <c r="G253" s="25">
@@ -8599,7 +8609,7 @@
       </c>
       <c r="H253" s="3"/>
     </row>
-    <row r="254" spans="1:8">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" s="25">
         <v>1040120</v>
       </c>
@@ -8611,7 +8621,7 @@
       </c>
       <c r="D254" s="3"/>
       <c r="E254" s="25" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F254" s="3"/>
       <c r="G254" s="25">
@@ -8619,7 +8629,7 @@
       </c>
       <c r="H254" s="3"/>
     </row>
-    <row r="255" spans="1:8">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" s="25">
         <v>1040130</v>
       </c>
@@ -8631,7 +8641,7 @@
       </c>
       <c r="D255" s="3"/>
       <c r="E255" s="25" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="F255" s="3"/>
       <c r="G255" s="25">
@@ -8639,7 +8649,7 @@
       </c>
       <c r="H255" s="3"/>
     </row>
-    <row r="256" spans="1:8">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" s="25">
         <v>1040140</v>
       </c>
@@ -8649,7 +8659,7 @@
       <c r="C256" s="3"/>
       <c r="D256" s="3"/>
       <c r="E256" s="25" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="F256" s="3"/>
       <c r="G256" s="25">
@@ -8657,7 +8667,7 @@
       </c>
       <c r="H256" s="3"/>
     </row>
-    <row r="257" spans="1:8">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" s="25">
         <v>1040150</v>
       </c>
@@ -8667,7 +8677,7 @@
       <c r="C257" s="25"/>
       <c r="D257" s="3"/>
       <c r="E257" s="25" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F257" s="3"/>
       <c r="G257" s="25">
@@ -8675,7 +8685,7 @@
       </c>
       <c r="H257" s="3"/>
     </row>
-    <row r="258" spans="1:8">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" s="25">
         <v>1040160</v>
       </c>
@@ -8685,13 +8695,13 @@
       <c r="C258" s="25"/>
       <c r="D258" s="3"/>
       <c r="E258" s="25" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F258" s="3"/>
       <c r="G258" s="25"/>
       <c r="H258" s="3"/>
     </row>
-    <row r="259" spans="1:8">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" s="25">
         <v>1040170</v>
       </c>
@@ -8701,7 +8711,7 @@
       <c r="C259" s="25"/>
       <c r="D259" s="3"/>
       <c r="E259" s="25" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F259" s="3"/>
       <c r="G259" s="3"/>
@@ -8709,7 +8719,7 @@
         <v>10210</v>
       </c>
     </row>
-    <row r="260" spans="1:8">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" s="25">
         <v>1040180</v>
       </c>
@@ -8721,7 +8731,7 @@
       </c>
       <c r="D260" s="3"/>
       <c r="E260" s="25" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="F260" s="3"/>
       <c r="G260" s="25">
@@ -8729,7 +8739,7 @@
       </c>
       <c r="H260" s="3"/>
     </row>
-    <row r="261" spans="1:8">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" s="25">
         <v>1040190</v>
       </c>
@@ -8741,7 +8751,7 @@
       </c>
       <c r="D261" s="3"/>
       <c r="E261" s="25" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F261" s="3"/>
       <c r="G261" s="25">
@@ -8749,7 +8759,7 @@
       </c>
       <c r="H261" s="3"/>
     </row>
-    <row r="262" spans="1:8">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" s="25">
         <v>1040200</v>
       </c>
@@ -8767,7 +8777,7 @@
       </c>
       <c r="H262" s="3"/>
     </row>
-    <row r="263" spans="1:8">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" s="25">
         <v>1040210</v>
       </c>
@@ -8779,7 +8789,7 @@
       </c>
       <c r="D263" s="3"/>
       <c r="E263" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="F263" s="3"/>
       <c r="G263" s="25">
@@ -8787,7 +8797,7 @@
       </c>
       <c r="H263" s="3"/>
     </row>
-    <row r="264" spans="1:8">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" s="25">
         <v>1040220</v>
       </c>
@@ -8799,7 +8809,7 @@
       </c>
       <c r="D264" s="3"/>
       <c r="E264" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="F264" s="3"/>
       <c r="G264" s="25">
@@ -8807,7 +8817,7 @@
       </c>
       <c r="H264" s="3"/>
     </row>
-    <row r="265" spans="1:8">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" s="25">
         <v>1040230</v>
       </c>
@@ -8819,7 +8829,7 @@
       </c>
       <c r="D265" s="3"/>
       <c r="E265" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F265" s="3"/>
       <c r="G265" s="25">
@@ -8827,7 +8837,7 @@
       </c>
       <c r="H265" s="3"/>
     </row>
-    <row r="266" spans="1:8">
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A266" s="25">
         <v>1040240</v>
       </c>
@@ -8839,7 +8849,7 @@
       </c>
       <c r="D266" s="3"/>
       <c r="E266" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="F266" s="3"/>
       <c r="G266" s="25">
@@ -8847,7 +8857,7 @@
       </c>
       <c r="H266" s="3"/>
     </row>
-    <row r="267" spans="1:8">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" s="25">
         <v>1040250</v>
       </c>
@@ -8859,7 +8869,7 @@
       </c>
       <c r="D267" s="3"/>
       <c r="E267" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="F267" s="3"/>
       <c r="G267" s="25">
@@ -8867,7 +8877,7 @@
       </c>
       <c r="H267" s="3"/>
     </row>
-    <row r="268" spans="1:8">
+    <row r="268" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A268" s="25">
         <v>1040260</v>
       </c>
@@ -8877,7 +8887,7 @@
       <c r="C268" s="3"/>
       <c r="D268" s="3"/>
       <c r="E268" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="F268" s="3"/>
       <c r="G268" s="25">
@@ -8885,7 +8895,7 @@
       </c>
       <c r="H268" s="3"/>
     </row>
-    <row r="269" spans="1:8">
+    <row r="269" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A269" s="25">
         <v>1040270</v>
       </c>
@@ -8895,7 +8905,7 @@
       <c r="C269" s="3"/>
       <c r="D269" s="3"/>
       <c r="E269" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="F269" s="3"/>
       <c r="G269" s="25">
@@ -8903,7 +8913,7 @@
       </c>
       <c r="H269" s="3"/>
     </row>
-    <row r="270" spans="1:8">
+    <row r="270" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A270" s="25">
         <v>1040280</v>
       </c>
@@ -8915,7 +8925,7 @@
       </c>
       <c r="D270" s="3"/>
       <c r="E270" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F270" s="3"/>
       <c r="G270" s="25">
@@ -8923,7 +8933,7 @@
       </c>
       <c r="H270" s="3"/>
     </row>
-    <row r="271" spans="1:8">
+    <row r="271" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A271" s="25">
         <v>1040290</v>
       </c>
@@ -8935,7 +8945,7 @@
       </c>
       <c r="D271" s="3"/>
       <c r="E271" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F271" s="3"/>
       <c r="G271" s="25">
@@ -8943,7 +8953,7 @@
       </c>
       <c r="H271" s="3"/>
     </row>
-    <row r="272" spans="1:8">
+    <row r="272" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A272" s="25">
         <v>1040300</v>
       </c>
@@ -8955,7 +8965,7 @@
       </c>
       <c r="D272" s="3"/>
       <c r="E272" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="F272" s="3"/>
       <c r="G272" s="25">
@@ -8963,7 +8973,7 @@
       </c>
       <c r="H272" s="3"/>
     </row>
-    <row r="273" spans="1:8">
+    <row r="273" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A273" s="25">
         <v>1040310</v>
       </c>
@@ -8975,7 +8985,7 @@
       </c>
       <c r="D273" s="3"/>
       <c r="E273" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="F273" s="3"/>
       <c r="G273" s="25">
@@ -8983,7 +8993,7 @@
       </c>
       <c r="H273" s="3"/>
     </row>
-    <row r="274" spans="1:8">
+    <row r="274" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A274" s="25">
         <v>1040320</v>
       </c>
@@ -8993,7 +9003,7 @@
       <c r="C274" s="3"/>
       <c r="D274" s="3"/>
       <c r="E274" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F274" s="3"/>
       <c r="G274" s="25">
@@ -9001,7 +9011,7 @@
       </c>
       <c r="H274" s="3"/>
     </row>
-    <row r="275" spans="1:8">
+    <row r="275" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A275" s="25">
         <v>1040330</v>
       </c>
@@ -9011,7 +9021,7 @@
       <c r="C275" s="3"/>
       <c r="D275" s="3"/>
       <c r="E275" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F275" s="3"/>
       <c r="G275" s="25">
@@ -9019,7 +9029,7 @@
       </c>
       <c r="H275" s="3"/>
     </row>
-    <row r="276" spans="1:8">
+    <row r="276" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A276" s="25">
         <v>1040340</v>
       </c>
@@ -9027,7 +9037,7 @@
       <c r="C276" s="25"/>
       <c r="D276" s="3"/>
       <c r="E276" s="25" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F276" s="3"/>
       <c r="G276" s="25">
@@ -9035,7 +9045,7 @@
       </c>
       <c r="H276" s="3"/>
     </row>
-    <row r="277" spans="1:8">
+    <row r="277" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A277" s="25">
         <v>1040350</v>
       </c>
@@ -9045,7 +9055,7 @@
       <c r="C277" s="25"/>
       <c r="D277" s="3"/>
       <c r="E277" s="25" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="F277" s="3"/>
       <c r="G277" s="25">
@@ -9053,7 +9063,7 @@
       </c>
       <c r="H277" s="3"/>
     </row>
-    <row r="278" spans="1:8">
+    <row r="278" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A278" s="25">
         <v>1040360</v>
       </c>
@@ -9063,16 +9073,16 @@
       <c r="C278" s="25"/>
       <c r="D278" s="3"/>
       <c r="E278" s="25" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="F278" s="3"/>
       <c r="G278" s="3"/>
       <c r="H278" s="3"/>
     </row>
-    <row r="279" spans="1:8">
+    <row r="279" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C279" s="30"/>
     </row>
-    <row r="280" spans="1:8">
+    <row r="280" spans="1:8" x14ac:dyDescent="0.3">
       <c r="C280" s="30"/>
     </row>
   </sheetData>
@@ -9084,19 +9094,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:H80"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="15.625" style="28" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="33.25" customWidth="1"/>
-    <col min="5" max="5" width="77.33203125" customWidth="1"/>
-    <col min="6" max="6" width="14.08203125" customWidth="1"/>
-    <col min="7" max="7" width="28.83203125" customWidth="1"/>
+    <col min="5" max="5" width="77.375" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
+    <col min="7" max="7" width="28.875" customWidth="1"/>
     <col min="8" max="8" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26.25" customHeight="1">
+    <row r="1" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
@@ -9122,7 +9132,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="3">
         <v>10101</v>
       </c>
@@ -9135,12 +9145,12 @@
         <v>146</v>
       </c>
       <c r="F2" s="3">
-        <v>101019</v>
+        <v>1010190</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="3">
         <v>10101</v>
       </c>
@@ -9153,34 +9163,34 @@
         <v>153</v>
       </c>
       <c r="F3" s="3">
-        <v>101026</v>
+        <v>1010260</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="3">
         <v>10201</v>
       </c>
       <c r="B4" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="C4" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="E4" s="3"/>
       <c r="F4" s="3">
-        <v>103014</v>
+        <v>1030140</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H4" s="3"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="3">
         <v>10201</v>
       </c>
@@ -9191,12 +9201,12 @@
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
       <c r="F5" s="3">
-        <v>103016</v>
+        <v>1030160</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="3">
         <v>10202</v>
       </c>
@@ -9209,69 +9219,69 @@
         <v>178</v>
       </c>
       <c r="F6" s="25">
-        <v>103018</v>
+        <v>1030180</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="3">
         <v>10202</v>
       </c>
       <c r="B7" s="31" t="s">
+        <v>416</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>418</v>
-      </c>
       <c r="E7" s="3" t="s">
-        <v>419</v>
+        <v>229</v>
       </c>
       <c r="F7" s="3">
-        <v>103034</v>
+        <v>1030610</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="3">
         <v>10202</v>
       </c>
       <c r="B8" s="31" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>421</v>
+      <c r="E8" s="57" t="s">
+        <v>605</v>
       </c>
       <c r="F8" s="3">
-        <v>103039</v>
+        <v>1031200</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="H8" s="3"/>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="3">
         <v>10203</v>
       </c>
       <c r="B9" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="D9" s="3" t="s">
         <v>414</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>415</v>
       </c>
       <c r="E9" s="3"/>
       <c r="F9" s="3">
@@ -9280,7 +9290,7 @@
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="3">
         <v>10203</v>
       </c>
@@ -9296,27 +9306,27 @@
       <c r="G10" s="3"/>
       <c r="H10" s="3"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="3">
         <v>10204</v>
       </c>
       <c r="B11" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D11" s="3" t="s">
-        <v>415</v>
-      </c>
       <c r="E11" s="3"/>
-      <c r="F11" s="3">
-        <v>103026</v>
+      <c r="F11" s="25">
+        <v>1030300</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="3">
         <v>10204</v>
       </c>
@@ -9326,13 +9336,13 @@
       <c r="C12" s="3"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="3">
-        <v>103027</v>
+      <c r="F12" s="25">
+        <v>1030310</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="3">
         <v>10205</v>
       </c>
@@ -9344,13 +9354,13 @@
       <c r="E13" s="3"/>
       <c r="F13" s="3"/>
       <c r="G13" s="3" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="3">
         <v>10206</v>
       </c>
@@ -9362,13 +9372,13 @@
       <c r="E14" s="3"/>
       <c r="F14" s="3"/>
       <c r="G14" s="3" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="3">
         <v>10207</v>
       </c>
@@ -9380,24 +9390,24 @@
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" ht="68">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="66" x14ac:dyDescent="0.3">
       <c r="A16" s="3">
         <v>10208</v>
       </c>
       <c r="B16" s="31" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="C16" s="32" t="s">
-        <v>430</v>
-      </c>
-      <c r="D16" s="32" t="s">
-        <v>431</v>
+        <v>427</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>601</v>
       </c>
       <c r="E16" s="3"/>
       <c r="F16" s="3">
@@ -9406,7 +9416,7 @@
       <c r="G16" s="3"/>
       <c r="H16" s="3"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="3">
         <v>10208</v>
       </c>
@@ -9422,55 +9432,55 @@
       <c r="G17" s="3"/>
       <c r="H17" s="3"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="3">
         <v>10209</v>
       </c>
       <c r="B18" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>414</v>
-      </c>
       <c r="D18" s="3" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="E18" s="3"/>
       <c r="F18" s="25">
         <v>1040030</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="H18" s="33" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A19" s="3">
         <v>10209</v>
       </c>
       <c r="B19" s="31" t="s">
-        <v>417</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>435</v>
+        <v>416</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>603</v>
+      </c>
+      <c r="D19" s="43" t="s">
+        <v>602</v>
       </c>
       <c r="E19" s="3"/>
       <c r="F19" s="25">
         <v>1040110</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="H19" s="33" t="s">
-        <v>437</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="3">
         <v>10209</v>
       </c>
@@ -9478,34 +9488,34 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
       <c r="E20" s="3"/>
       <c r="F20" s="25">
         <v>1040170</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="H20" s="33" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="3">
         <v>10210</v>
       </c>
       <c r="B21" s="31" t="s">
+        <v>412</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C21" s="3" t="s">
-        <v>414</v>
-      </c>
       <c r="D21" s="3" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="E21" s="3"/>
       <c r="F21" s="3">
@@ -9514,7 +9524,7 @@
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="3">
         <v>10210</v>
       </c>
@@ -9530,202 +9540,203 @@
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B23"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B24"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B25"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B26"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B27"/>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B28"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B29"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B30"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B31"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B32"/>
     </row>
-    <row r="33" spans="2:2">
+    <row r="33" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B33"/>
     </row>
-    <row r="34" spans="2:2">
+    <row r="34" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B34"/>
     </row>
-    <row r="35" spans="2:2">
+    <row r="35" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B35"/>
     </row>
-    <row r="36" spans="2:2">
+    <row r="36" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B36"/>
     </row>
-    <row r="37" spans="2:2">
+    <row r="37" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B37"/>
     </row>
-    <row r="38" spans="2:2">
+    <row r="38" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B38"/>
     </row>
-    <row r="39" spans="2:2">
+    <row r="39" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B39"/>
     </row>
-    <row r="40" spans="2:2">
+    <row r="40" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B40"/>
     </row>
-    <row r="41" spans="2:2">
+    <row r="41" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B41"/>
     </row>
-    <row r="42" spans="2:2">
+    <row r="42" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B42"/>
     </row>
-    <row r="43" spans="2:2">
+    <row r="43" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B43"/>
     </row>
-    <row r="44" spans="2:2">
+    <row r="44" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B44"/>
     </row>
-    <row r="45" spans="2:2">
+    <row r="45" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B45"/>
     </row>
-    <row r="46" spans="2:2">
+    <row r="46" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B46"/>
     </row>
-    <row r="47" spans="2:2">
+    <row r="47" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B47"/>
     </row>
-    <row r="48" spans="2:2">
+    <row r="48" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B48"/>
     </row>
-    <row r="49" spans="2:2">
+    <row r="49" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B49"/>
     </row>
-    <row r="50" spans="2:2">
+    <row r="50" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B50"/>
     </row>
-    <row r="51" spans="2:2">
+    <row r="51" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B51"/>
     </row>
-    <row r="52" spans="2:2">
+    <row r="52" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B52"/>
     </row>
-    <row r="53" spans="2:2">
+    <row r="53" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B53"/>
     </row>
-    <row r="54" spans="2:2">
+    <row r="54" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B54"/>
     </row>
-    <row r="55" spans="2:2">
+    <row r="55" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B55"/>
     </row>
-    <row r="56" spans="2:2">
+    <row r="56" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B56"/>
     </row>
-    <row r="57" spans="2:2">
+    <row r="57" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B57"/>
     </row>
-    <row r="58" spans="2:2">
+    <row r="58" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B58"/>
     </row>
-    <row r="59" spans="2:2">
+    <row r="59" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B59"/>
     </row>
-    <row r="60" spans="2:2">
+    <row r="60" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B60"/>
     </row>
-    <row r="61" spans="2:2">
+    <row r="61" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B61"/>
     </row>
-    <row r="62" spans="2:2">
+    <row r="62" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B62"/>
     </row>
-    <row r="63" spans="2:2">
+    <row r="63" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B63"/>
     </row>
-    <row r="64" spans="2:2">
+    <row r="64" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B64"/>
     </row>
-    <row r="65" spans="2:2">
+    <row r="65" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B65"/>
     </row>
-    <row r="66" spans="2:2">
+    <row r="66" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B66"/>
     </row>
-    <row r="67" spans="2:2">
+    <row r="67" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B67"/>
     </row>
-    <row r="68" spans="2:2">
+    <row r="68" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B68"/>
     </row>
-    <row r="69" spans="2:2">
+    <row r="69" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B69"/>
     </row>
-    <row r="70" spans="2:2">
+    <row r="70" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B70"/>
     </row>
-    <row r="71" spans="2:2">
+    <row r="71" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B71"/>
     </row>
-    <row r="72" spans="2:2">
+    <row r="72" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B72"/>
     </row>
-    <row r="73" spans="2:2">
+    <row r="73" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B73"/>
     </row>
-    <row r="74" spans="2:2">
+    <row r="74" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B74"/>
     </row>
-    <row r="75" spans="2:2">
+    <row r="75" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B75"/>
     </row>
-    <row r="76" spans="2:2">
+    <row r="76" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B76"/>
     </row>
-    <row r="77" spans="2:2">
+    <row r="77" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B77"/>
     </row>
-    <row r="78" spans="2:2">
+    <row r="78" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B78"/>
     </row>
-    <row r="79" spans="2:2">
+    <row r="79" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B79"/>
     </row>
-    <row r="80" spans="2:2">
+    <row r="80" spans="2:2" x14ac:dyDescent="0.3">
       <c r="B80"/>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:H119"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.58203125" customWidth="1"/>
+    <col min="1" max="1" width="14.625" customWidth="1"/>
     <col min="2" max="2" width="10.25" customWidth="1"/>
     <col min="3" max="3" width="16.5" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
     <col min="5" max="5" width="109.25" customWidth="1"/>
-    <col min="6" max="6" width="27.58203125" customWidth="1"/>
-    <col min="7" max="7" width="14.08203125" customWidth="1"/>
-    <col min="8" max="8" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="27.625" customWidth="1"/>
+    <col min="7" max="7" width="14.125" customWidth="1"/>
+    <col min="8" max="8" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="13" t="s">
         <v>33</v>
       </c>
@@ -9751,7 +9762,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <v>1050010</v>
       </c>
@@ -9761,7 +9772,7 @@
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="F2" s="37"/>
       <c r="G2" s="37">
@@ -9769,7 +9780,7 @@
       </c>
       <c r="H2" s="37"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="37">
         <v>1050020</v>
       </c>
@@ -9777,11 +9788,11 @@
         <v>0</v>
       </c>
       <c r="C3" s="37" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D3" s="37"/>
       <c r="E3" s="37" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="F3" s="37"/>
       <c r="G3" s="37">
@@ -9789,7 +9800,7 @@
       </c>
       <c r="H3" s="37"/>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="37">
         <v>1050030</v>
       </c>
@@ -9799,7 +9810,7 @@
       <c r="C4" s="37"/>
       <c r="D4" s="37"/>
       <c r="E4" s="37" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="F4" s="37"/>
       <c r="G4" s="37">
@@ -9807,7 +9818,7 @@
       </c>
       <c r="H4" s="37"/>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>1050040</v>
       </c>
@@ -9815,11 +9826,11 @@
         <v>0</v>
       </c>
       <c r="C5" s="37" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D5" s="37"/>
       <c r="E5" s="37" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="F5" s="37"/>
       <c r="G5" s="37">
@@ -9827,7 +9838,7 @@
       </c>
       <c r="H5" s="37"/>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>1050050</v>
       </c>
@@ -9835,11 +9846,11 @@
         <v>0</v>
       </c>
       <c r="C6" s="37" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D6" s="37"/>
       <c r="E6" s="37" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
       <c r="F6" s="37"/>
       <c r="G6" s="37">
@@ -9847,7 +9858,7 @@
       </c>
       <c r="H6" s="37"/>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>1050060</v>
       </c>
@@ -9859,7 +9870,7 @@
       </c>
       <c r="D7" s="37"/>
       <c r="E7" s="37" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="F7" s="37"/>
       <c r="G7" s="37">
@@ -9867,7 +9878,7 @@
       </c>
       <c r="H7" s="37"/>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>1050070</v>
       </c>
@@ -9877,7 +9888,7 @@
       <c r="C8" s="37"/>
       <c r="D8" s="37"/>
       <c r="E8" s="37" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="F8" s="37"/>
       <c r="G8" s="37"/>
@@ -9885,7 +9896,7 @@
         <v>10501</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>1050080</v>
       </c>
@@ -9895,7 +9906,7 @@
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
       <c r="E9" s="37" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F9" s="37"/>
       <c r="G9" s="37">
@@ -9903,7 +9914,7 @@
       </c>
       <c r="H9" s="37"/>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>1050090</v>
       </c>
@@ -9911,11 +9922,11 @@
         <v>0</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D10" s="37"/>
       <c r="E10" s="37" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="F10" s="37"/>
       <c r="G10" s="37">
@@ -9923,7 +9934,7 @@
       </c>
       <c r="H10" s="37"/>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>1050100</v>
       </c>
@@ -9935,7 +9946,7 @@
       </c>
       <c r="D11" s="37"/>
       <c r="E11" s="37" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="F11" s="37"/>
       <c r="G11" s="37">
@@ -9943,7 +9954,7 @@
       </c>
       <c r="H11" s="37"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>1050110</v>
       </c>
@@ -9953,7 +9964,7 @@
       <c r="C12" s="37"/>
       <c r="D12" s="37"/>
       <c r="E12" s="37" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="F12" s="37"/>
       <c r="G12" s="37">
@@ -9961,7 +9972,7 @@
       </c>
       <c r="H12" s="37"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>1050120</v>
       </c>
@@ -9969,11 +9980,11 @@
         <v>0</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D13" s="37"/>
       <c r="E13" s="37" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="F13" s="37"/>
       <c r="G13" s="37">
@@ -9981,7 +9992,7 @@
       </c>
       <c r="H13" s="37"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>1050130</v>
       </c>
@@ -9993,7 +10004,7 @@
       </c>
       <c r="D14" s="37"/>
       <c r="E14" s="37" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="F14" s="37"/>
       <c r="G14" s="37">
@@ -10001,7 +10012,7 @@
       </c>
       <c r="H14" s="37"/>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>1050140</v>
       </c>
@@ -10011,7 +10022,7 @@
       <c r="C15" s="37"/>
       <c r="D15" s="37"/>
       <c r="E15" s="37" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="F15" s="37"/>
       <c r="G15" s="37">
@@ -10019,7 +10030,7 @@
       </c>
       <c r="H15" s="37"/>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>1050150</v>
       </c>
@@ -10029,7 +10040,7 @@
       <c r="C16" s="37"/>
       <c r="D16" s="37"/>
       <c r="E16" s="37" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
       <c r="F16" s="37"/>
       <c r="G16" s="37">
@@ -10037,7 +10048,7 @@
       </c>
       <c r="H16" s="37"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>1050160</v>
       </c>
@@ -10049,7 +10060,7 @@
       </c>
       <c r="D17" s="37"/>
       <c r="E17" s="37" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="F17" s="37"/>
       <c r="G17" s="37">
@@ -10057,7 +10068,7 @@
       </c>
       <c r="H17" s="37"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>1050170</v>
       </c>
@@ -10067,7 +10078,7 @@
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
       <c r="E18" s="37" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="F18" s="37"/>
       <c r="G18" s="37"/>
@@ -10075,7 +10086,7 @@
         <v>10502</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>1060010</v>
       </c>
@@ -10085,7 +10096,7 @@
       <c r="C19" s="37"/>
       <c r="D19" s="37"/>
       <c r="E19" s="37" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="F19" s="37"/>
       <c r="G19" s="37">
@@ -10093,7 +10104,7 @@
       </c>
       <c r="H19" s="37"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>1060020</v>
       </c>
@@ -10105,7 +10116,7 @@
       </c>
       <c r="D20" s="37"/>
       <c r="E20" s="37" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="F20" s="37"/>
       <c r="G20" s="37">
@@ -10113,7 +10124,7 @@
       </c>
       <c r="H20" s="37"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>1060030</v>
       </c>
@@ -10125,7 +10136,7 @@
       </c>
       <c r="D21" s="37"/>
       <c r="E21" s="37" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="F21" s="37"/>
       <c r="G21" s="37">
@@ -10133,7 +10144,7 @@
       </c>
       <c r="H21" s="37"/>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>1060040</v>
       </c>
@@ -10143,7 +10154,7 @@
       <c r="C22" s="37"/>
       <c r="D22" s="37"/>
       <c r="E22" s="37" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="F22" s="37"/>
       <c r="G22" s="37">
@@ -10151,7 +10162,7 @@
       </c>
       <c r="H22" s="37"/>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>1060050</v>
       </c>
@@ -10159,11 +10170,11 @@
         <v>0</v>
       </c>
       <c r="C23" s="37" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D23" s="37"/>
       <c r="E23" s="37" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="F23" s="37"/>
       <c r="G23" s="37">
@@ -10171,7 +10182,7 @@
       </c>
       <c r="H23" s="37"/>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>1060060</v>
       </c>
@@ -10183,7 +10194,7 @@
       </c>
       <c r="D24" s="37"/>
       <c r="E24" s="37" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
       <c r="F24" s="37"/>
       <c r="G24" s="37">
@@ -10191,7 +10202,7 @@
       </c>
       <c r="H24" s="37"/>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>1060070</v>
       </c>
@@ -10199,11 +10210,11 @@
         <v>0</v>
       </c>
       <c r="C25" s="37" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D25" s="37"/>
       <c r="E25" s="37" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="F25" s="37"/>
       <c r="G25" s="37">
@@ -10211,7 +10222,7 @@
       </c>
       <c r="H25" s="37"/>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="37">
         <v>1060080</v>
       </c>
@@ -10223,7 +10234,7 @@
       </c>
       <c r="D26" s="37"/>
       <c r="E26" s="37" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="F26" s="37"/>
       <c r="G26" s="37">
@@ -10231,7 +10242,7 @@
       </c>
       <c r="H26" s="37"/>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>1060090</v>
       </c>
@@ -10241,7 +10252,7 @@
       <c r="C27" s="37"/>
       <c r="D27" s="37"/>
       <c r="E27" s="37" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="F27" s="37"/>
       <c r="G27" s="37"/>
@@ -10249,7 +10260,7 @@
         <v>10601</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>1060100</v>
       </c>
@@ -10259,7 +10270,7 @@
       <c r="C28" s="37"/>
       <c r="D28" s="37"/>
       <c r="E28" s="37" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F28" s="37"/>
       <c r="G28" s="37">
@@ -10267,7 +10278,7 @@
       </c>
       <c r="H28" s="37"/>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>1060110</v>
       </c>
@@ -10275,11 +10286,11 @@
         <v>0</v>
       </c>
       <c r="C29" s="37" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D29" s="37"/>
       <c r="E29" s="37" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="F29" s="37"/>
       <c r="G29" s="37">
@@ -10287,7 +10298,7 @@
       </c>
       <c r="H29" s="37"/>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>1060120</v>
       </c>
@@ -10299,7 +10310,7 @@
       </c>
       <c r="D30" s="37"/>
       <c r="E30" s="37" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F30" s="37"/>
       <c r="G30" s="37">
@@ -10307,7 +10318,7 @@
       </c>
       <c r="H30" s="37"/>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>1060130</v>
       </c>
@@ -10315,11 +10326,11 @@
         <v>0</v>
       </c>
       <c r="C31" s="37" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D31" s="37"/>
       <c r="E31" s="37" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="F31" s="37"/>
       <c r="G31" s="37">
@@ -10327,7 +10338,7 @@
       </c>
       <c r="H31" s="37"/>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>1060140</v>
       </c>
@@ -10337,7 +10348,7 @@
       <c r="C32" s="37"/>
       <c r="D32" s="37"/>
       <c r="E32" s="37" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F32" s="37"/>
       <c r="G32" s="37">
@@ -10345,7 +10356,7 @@
       </c>
       <c r="H32" s="37"/>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>1060150</v>
       </c>
@@ -10353,11 +10364,11 @@
         <v>0</v>
       </c>
       <c r="C33" s="37" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D33" s="37"/>
       <c r="E33" s="37" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
       <c r="F33" s="37"/>
       <c r="G33" s="37">
@@ -10365,7 +10376,7 @@
       </c>
       <c r="H33" s="37"/>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>1060160</v>
       </c>
@@ -10373,11 +10384,11 @@
         <v>0</v>
       </c>
       <c r="C34" s="37" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D34" s="37"/>
       <c r="E34" s="37" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
       <c r="F34" s="37"/>
       <c r="G34" s="37">
@@ -10385,7 +10396,7 @@
       </c>
       <c r="H34" s="37"/>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>1060170</v>
       </c>
@@ -10395,7 +10406,7 @@
       <c r="C35" s="37"/>
       <c r="D35" s="37"/>
       <c r="E35" s="37" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
       <c r="F35" s="37"/>
       <c r="G35" s="37">
@@ -10403,7 +10414,7 @@
       </c>
       <c r="H35" s="37"/>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>1060180</v>
       </c>
@@ -10411,11 +10422,11 @@
         <v>0</v>
       </c>
       <c r="C36" s="37" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D36" s="37"/>
       <c r="E36" s="37" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
       <c r="F36" s="37"/>
       <c r="G36" s="37">
@@ -10423,7 +10434,7 @@
       </c>
       <c r="H36" s="37"/>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>1060190</v>
       </c>
@@ -10435,7 +10446,7 @@
       </c>
       <c r="D37" s="37"/>
       <c r="E37" s="37" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
       <c r="F37" s="37"/>
       <c r="G37" s="37">
@@ -10443,7 +10454,7 @@
       </c>
       <c r="H37" s="37"/>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>1060200</v>
       </c>
@@ -10453,7 +10464,7 @@
       <c r="C38" s="37"/>
       <c r="D38" s="37"/>
       <c r="E38" s="37" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
       <c r="F38" s="37"/>
       <c r="G38" s="37">
@@ -10461,7 +10472,7 @@
       </c>
       <c r="H38" s="37"/>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>1060210</v>
       </c>
@@ -10469,11 +10480,11 @@
         <v>0</v>
       </c>
       <c r="C39" s="37" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D39" s="37"/>
       <c r="E39" s="37" t="s">
-        <v>482</v>
+        <v>477</v>
       </c>
       <c r="F39" s="37"/>
       <c r="G39" s="37">
@@ -10481,7 +10492,7 @@
       </c>
       <c r="H39" s="37"/>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>1060220</v>
       </c>
@@ -10489,11 +10500,11 @@
         <v>0</v>
       </c>
       <c r="C40" s="37" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D40" s="37"/>
       <c r="E40" s="37" t="s">
-        <v>483</v>
+        <v>478</v>
       </c>
       <c r="F40" s="37"/>
       <c r="G40" s="37">
@@ -10501,7 +10512,7 @@
       </c>
       <c r="H40" s="37"/>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>1060230</v>
       </c>
@@ -10511,7 +10522,7 @@
       <c r="C41" s="37"/>
       <c r="D41" s="37"/>
       <c r="E41" s="37" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="F41" s="37"/>
       <c r="G41" s="37"/>
@@ -10519,7 +10530,7 @@
         <v>10602</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>1070010</v>
       </c>
@@ -10529,7 +10540,7 @@
       <c r="C42" s="37"/>
       <c r="D42" s="37"/>
       <c r="E42" s="37" t="s">
-        <v>485</v>
+        <v>480</v>
       </c>
       <c r="F42" s="37"/>
       <c r="G42" s="37">
@@ -10537,7 +10548,7 @@
       </c>
       <c r="H42" s="37"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>1070020</v>
       </c>
@@ -10545,11 +10556,11 @@
         <v>0</v>
       </c>
       <c r="C43" s="37" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D43" s="37"/>
       <c r="E43" s="37" t="s">
-        <v>486</v>
+        <v>481</v>
       </c>
       <c r="F43" s="37"/>
       <c r="G43" s="37">
@@ -10557,7 +10568,7 @@
       </c>
       <c r="H43" s="37"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>1070030</v>
       </c>
@@ -10565,11 +10576,11 @@
         <v>0</v>
       </c>
       <c r="C44" s="37" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D44" s="37"/>
       <c r="E44" s="37" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="F44" s="37"/>
       <c r="G44" s="37">
@@ -10577,7 +10588,7 @@
       </c>
       <c r="H44" s="37"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="37">
         <v>1070040</v>
       </c>
@@ -10589,7 +10600,7 @@
       </c>
       <c r="D45" s="37"/>
       <c r="E45" s="37" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="F45" s="37"/>
       <c r="G45" s="37">
@@ -10597,7 +10608,7 @@
       </c>
       <c r="H45" s="37"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>1070050</v>
       </c>
@@ -10609,7 +10620,7 @@
       </c>
       <c r="D46" s="37"/>
       <c r="E46" s="37" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="F46" s="37"/>
       <c r="G46" s="37">
@@ -10617,7 +10628,7 @@
       </c>
       <c r="H46" s="37"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="37">
         <v>1070060</v>
       </c>
@@ -10627,7 +10638,7 @@
       <c r="C47" s="37"/>
       <c r="D47" s="37"/>
       <c r="E47" s="37" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="F47" s="37"/>
       <c r="G47" s="37">
@@ -10635,7 +10646,7 @@
       </c>
       <c r="H47" s="37"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="37">
         <v>1070070</v>
       </c>
@@ -10647,7 +10658,7 @@
       </c>
       <c r="D48" s="37"/>
       <c r="E48" s="37" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="F48" s="37"/>
       <c r="G48" s="37">
@@ -10655,7 +10666,7 @@
       </c>
       <c r="H48" s="37"/>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" s="37">
         <v>1070080</v>
       </c>
@@ -10667,7 +10678,7 @@
       </c>
       <c r="D49" s="37"/>
       <c r="E49" s="37" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="F49" s="37"/>
       <c r="G49" s="37">
@@ -10675,7 +10686,7 @@
       </c>
       <c r="H49" s="37"/>
     </row>
-    <row r="50" spans="1:8">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" s="37">
         <v>1070090</v>
       </c>
@@ -10685,7 +10696,7 @@
       <c r="C50" s="37"/>
       <c r="D50" s="37"/>
       <c r="E50" s="37" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="F50" s="37"/>
       <c r="G50" s="37"/>
@@ -10693,7 +10704,7 @@
         <v>10701</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" s="37">
         <v>1070100</v>
       </c>
@@ -10703,7 +10714,7 @@
       <c r="C51" s="37"/>
       <c r="D51" s="37"/>
       <c r="E51" s="37" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F51" s="37"/>
       <c r="G51" s="37">
@@ -10711,7 +10722,7 @@
       </c>
       <c r="H51" s="37"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" s="37">
         <v>1070110</v>
       </c>
@@ -10723,7 +10734,7 @@
       </c>
       <c r="D52" s="37"/>
       <c r="E52" s="37" t="s">
-        <v>495</v>
+        <v>490</v>
       </c>
       <c r="F52" s="37"/>
       <c r="G52" s="37">
@@ -10731,7 +10742,7 @@
       </c>
       <c r="H52" s="37"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" s="37">
         <v>1070120</v>
       </c>
@@ -10739,11 +10750,11 @@
         <v>0</v>
       </c>
       <c r="C53" s="37" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="D53" s="37"/>
       <c r="E53" s="37" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="F53" s="37"/>
       <c r="G53" s="37">
@@ -10751,7 +10762,7 @@
       </c>
       <c r="H53" s="37"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" s="37">
         <v>1070130</v>
       </c>
@@ -10761,7 +10772,7 @@
       <c r="C54" s="37"/>
       <c r="D54" s="37"/>
       <c r="E54" s="37" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="F54" s="37"/>
       <c r="G54" s="37">
@@ -10769,7 +10780,7 @@
       </c>
       <c r="H54" s="37"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" s="37">
         <v>1070140</v>
       </c>
@@ -10779,7 +10790,7 @@
       <c r="C55" s="37"/>
       <c r="D55" s="37"/>
       <c r="E55" s="37" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F55" s="37"/>
       <c r="G55" s="37">
@@ -10787,7 +10798,7 @@
       </c>
       <c r="H55" s="37"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" s="37">
         <v>1070150</v>
       </c>
@@ -10795,11 +10806,11 @@
         <v>0</v>
       </c>
       <c r="C56" s="37" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D56" s="37"/>
       <c r="E56" s="37" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="F56" s="37"/>
       <c r="G56" s="37">
@@ -10807,7 +10818,7 @@
       </c>
       <c r="H56" s="37"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" s="37">
         <v>1070160</v>
       </c>
@@ -10819,7 +10830,7 @@
       </c>
       <c r="D57" s="37"/>
       <c r="E57" s="37" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F57" s="37"/>
       <c r="G57" s="37">
@@ -10827,7 +10838,7 @@
       </c>
       <c r="H57" s="37"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" s="37">
         <v>1070170</v>
       </c>
@@ -10839,7 +10850,7 @@
       </c>
       <c r="D58" s="37"/>
       <c r="E58" s="37" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="F58" s="37"/>
       <c r="G58" s="37">
@@ -10847,7 +10858,7 @@
       </c>
       <c r="H58" s="37"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" s="37">
         <v>1070200</v>
       </c>
@@ -10857,7 +10868,7 @@
       <c r="C59" s="37"/>
       <c r="D59" s="37"/>
       <c r="E59" s="37" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="F59" s="37"/>
       <c r="G59" s="37">
@@ -10865,7 +10876,7 @@
       </c>
       <c r="H59" s="37"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" s="37">
         <v>1070210</v>
       </c>
@@ -10873,11 +10884,11 @@
         <v>0</v>
       </c>
       <c r="C60" s="37" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="D60" s="37"/>
       <c r="E60" s="37" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F60" s="37"/>
       <c r="G60" s="37">
@@ -10885,7 +10896,7 @@
       </c>
       <c r="H60" s="37"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" s="37">
         <v>1070220</v>
       </c>
@@ -10893,11 +10904,11 @@
         <v>0</v>
       </c>
       <c r="C61" s="37" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="D61" s="37"/>
       <c r="E61" s="37" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="F61" s="37"/>
       <c r="G61" s="37">
@@ -10905,7 +10916,7 @@
       </c>
       <c r="H61" s="37"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="37">
         <v>1070230</v>
       </c>
@@ -10915,7 +10926,7 @@
       <c r="C62" s="37"/>
       <c r="D62" s="37"/>
       <c r="E62" s="37" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="F62" s="37"/>
       <c r="G62" s="37"/>
@@ -10923,7 +10934,7 @@
         <v>10702</v>
       </c>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" s="37">
         <v>1080010</v>
       </c>
@@ -10933,7 +10944,7 @@
       <c r="C63" s="37"/>
       <c r="D63" s="37"/>
       <c r="E63" s="37" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="F63" s="37"/>
       <c r="G63" s="37">
@@ -10941,7 +10952,7 @@
       </c>
       <c r="H63" s="37"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" s="37">
         <v>1080020</v>
       </c>
@@ -10949,11 +10960,11 @@
         <v>0</v>
       </c>
       <c r="C64" s="37" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D64" s="37"/>
       <c r="E64" s="37" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="F64" s="37"/>
       <c r="G64" s="37">
@@ -10961,7 +10972,7 @@
       </c>
       <c r="H64" s="37"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" s="37">
         <v>1080030</v>
       </c>
@@ -10971,7 +10982,7 @@
       <c r="C65" s="37"/>
       <c r="D65" s="37"/>
       <c r="E65" s="37" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="F65" s="37"/>
       <c r="G65" s="37">
@@ -10979,7 +10990,7 @@
       </c>
       <c r="H65" s="37"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" s="37">
         <v>1080040</v>
       </c>
@@ -10987,11 +10998,11 @@
         <v>0</v>
       </c>
       <c r="C66" s="37" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D66" s="37"/>
       <c r="E66" s="37" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="F66" s="37"/>
       <c r="G66" s="37">
@@ -10999,7 +11010,7 @@
       </c>
       <c r="H66" s="37"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" s="37">
         <v>1080050</v>
       </c>
@@ -11011,7 +11022,7 @@
       </c>
       <c r="D67" s="37"/>
       <c r="E67" s="37" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="F67" s="37"/>
       <c r="G67" s="37">
@@ -11019,7 +11030,7 @@
       </c>
       <c r="H67" s="37"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" s="37">
         <v>1080060</v>
       </c>
@@ -11031,7 +11042,7 @@
       </c>
       <c r="D68" s="37"/>
       <c r="E68" s="37" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="F68" s="37"/>
       <c r="G68" s="37">
@@ -11039,7 +11050,7 @@
       </c>
       <c r="H68" s="37"/>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" s="37">
         <v>1080070</v>
       </c>
@@ -11049,7 +11060,7 @@
       <c r="C69" s="37"/>
       <c r="D69" s="37"/>
       <c r="E69" s="37" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="F69" s="37"/>
       <c r="G69" s="37"/>
@@ -11057,7 +11068,7 @@
         <v>10801</v>
       </c>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" s="37">
         <v>1080080</v>
       </c>
@@ -11067,7 +11078,7 @@
       <c r="C70" s="37"/>
       <c r="D70" s="37"/>
       <c r="E70" s="37" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F70" s="37"/>
       <c r="G70" s="37">
@@ -11075,7 +11086,7 @@
       </c>
       <c r="H70" s="37"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" s="37">
         <v>1080090</v>
       </c>
@@ -11087,7 +11098,7 @@
       </c>
       <c r="D71" s="37"/>
       <c r="E71" s="37" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="F71" s="37"/>
       <c r="G71" s="37">
@@ -11095,7 +11106,7 @@
       </c>
       <c r="H71" s="37"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" s="37">
         <v>1080100</v>
       </c>
@@ -11107,7 +11118,7 @@
       </c>
       <c r="D72" s="37"/>
       <c r="E72" s="37" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="F72" s="37"/>
       <c r="G72" s="37">
@@ -11115,7 +11126,7 @@
       </c>
       <c r="H72" s="37"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" s="37">
         <v>1080110</v>
       </c>
@@ -11125,7 +11136,7 @@
       <c r="C73" s="37"/>
       <c r="D73" s="37"/>
       <c r="E73" s="37" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="F73" s="37"/>
       <c r="G73" s="37">
@@ -11133,7 +11144,7 @@
       </c>
       <c r="H73" s="37"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" s="37">
         <v>1080120</v>
       </c>
@@ -11145,7 +11156,7 @@
       </c>
       <c r="D74" s="37"/>
       <c r="E74" s="37" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="F74" s="37"/>
       <c r="G74" s="37">
@@ -11153,7 +11164,7 @@
       </c>
       <c r="H74" s="37"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" s="37">
         <v>1080130</v>
       </c>
@@ -11163,7 +11174,7 @@
       <c r="C75" s="37"/>
       <c r="D75" s="37"/>
       <c r="E75" s="37" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="F75" s="37"/>
       <c r="G75" s="37">
@@ -11171,7 +11182,7 @@
       </c>
       <c r="H75" s="37"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" s="37">
         <v>1080140</v>
       </c>
@@ -11181,7 +11192,7 @@
       <c r="C76" s="37"/>
       <c r="D76" s="37"/>
       <c r="E76" s="37" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="F76" s="37"/>
       <c r="G76" s="37">
@@ -11189,7 +11200,7 @@
       </c>
       <c r="H76" s="37"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" s="37">
         <v>1080150</v>
       </c>
@@ -11201,7 +11212,7 @@
       </c>
       <c r="D77" s="37"/>
       <c r="E77" s="37" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F77" s="37"/>
       <c r="G77" s="37">
@@ -11209,7 +11220,7 @@
       </c>
       <c r="H77" s="37"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" s="37">
         <v>1080160</v>
       </c>
@@ -11219,7 +11230,7 @@
       <c r="C78" s="37"/>
       <c r="D78" s="37"/>
       <c r="E78" s="37" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="F78" s="37"/>
       <c r="G78" s="37"/>
@@ -11227,7 +11238,7 @@
         <v>10802</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" s="37">
         <v>1090010</v>
       </c>
@@ -11237,7 +11248,7 @@
       <c r="C79" s="37"/>
       <c r="D79" s="37"/>
       <c r="E79" s="37" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="F79" s="37"/>
       <c r="G79" s="37">
@@ -11245,7 +11256,7 @@
       </c>
       <c r="H79" s="37"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" s="37">
         <v>1090020</v>
       </c>
@@ -11257,7 +11268,7 @@
       </c>
       <c r="D80" s="37"/>
       <c r="E80" s="37" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="F80" s="37"/>
       <c r="G80" s="37">
@@ -11265,7 +11276,7 @@
       </c>
       <c r="H80" s="37"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="37">
         <v>1090030</v>
       </c>
@@ -11277,7 +11288,7 @@
       </c>
       <c r="D81" s="37"/>
       <c r="E81" s="37" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="F81" s="37"/>
       <c r="G81" s="37">
@@ -11285,7 +11296,7 @@
       </c>
       <c r="H81" s="37"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="37">
         <v>1090040</v>
       </c>
@@ -11293,11 +11304,11 @@
         <v>0</v>
       </c>
       <c r="C82" s="37" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="D82" s="37"/>
       <c r="E82" s="37" t="s">
-        <v>526</v>
+        <v>521</v>
       </c>
       <c r="F82" s="37"/>
       <c r="G82" s="37">
@@ -11305,7 +11316,7 @@
       </c>
       <c r="H82" s="37"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="37">
         <v>1090050</v>
       </c>
@@ -11317,7 +11328,7 @@
       </c>
       <c r="D83" s="37"/>
       <c r="E83" s="37" t="s">
-        <v>527</v>
+        <v>522</v>
       </c>
       <c r="F83" s="37"/>
       <c r="G83" s="37">
@@ -11325,7 +11336,7 @@
       </c>
       <c r="H83" s="37"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" s="37">
         <v>1090060</v>
       </c>
@@ -11335,7 +11346,7 @@
       <c r="C84" s="37"/>
       <c r="D84" s="37"/>
       <c r="E84" s="37" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="F84" s="37"/>
       <c r="G84" s="37">
@@ -11343,7 +11354,7 @@
       </c>
       <c r="H84" s="37"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" s="37">
         <v>1090070</v>
       </c>
@@ -11353,7 +11364,7 @@
       <c r="C85" s="37"/>
       <c r="D85" s="37"/>
       <c r="E85" s="37" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="F85" s="37"/>
       <c r="G85" s="37">
@@ -11361,7 +11372,7 @@
       </c>
       <c r="H85" s="37"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" s="37">
         <v>1090080</v>
       </c>
@@ -11373,7 +11384,7 @@
       </c>
       <c r="D86" s="37"/>
       <c r="E86" s="37" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="F86" s="37"/>
       <c r="G86" s="37">
@@ -11381,7 +11392,7 @@
       </c>
       <c r="H86" s="37"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" s="37">
         <v>1090090</v>
       </c>
@@ -11391,7 +11402,7 @@
       <c r="C87" s="37"/>
       <c r="D87" s="37"/>
       <c r="E87" s="37" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="F87" s="37"/>
       <c r="G87" s="37"/>
@@ -11399,7 +11410,7 @@
         <v>10901</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="37">
         <v>1090100</v>
       </c>
@@ -11409,7 +11420,7 @@
       <c r="C88" s="37"/>
       <c r="D88" s="37"/>
       <c r="E88" s="37" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="F88" s="37"/>
       <c r="G88" s="37">
@@ -11417,7 +11428,7 @@
       </c>
       <c r="H88" s="37"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" s="37">
         <v>1090110</v>
       </c>
@@ -11429,7 +11440,7 @@
       </c>
       <c r="D89" s="37"/>
       <c r="E89" s="37" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="F89" s="37"/>
       <c r="G89" s="37">
@@ -11437,7 +11448,7 @@
       </c>
       <c r="H89" s="37"/>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" s="37">
         <v>1090120</v>
       </c>
@@ -11447,7 +11458,7 @@
       <c r="C90" s="37"/>
       <c r="D90" s="37"/>
       <c r="E90" s="37" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="F90" s="37"/>
       <c r="G90" s="37">
@@ -11455,7 +11466,7 @@
       </c>
       <c r="H90" s="37"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" s="37">
         <v>1090130</v>
       </c>
@@ -11463,11 +11474,11 @@
         <v>0</v>
       </c>
       <c r="C91" s="37" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="D91" s="37"/>
       <c r="E91" s="37" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="F91" s="37"/>
       <c r="G91" s="37">
@@ -11475,7 +11486,7 @@
       </c>
       <c r="H91" s="37"/>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="37">
         <v>1090140</v>
       </c>
@@ -11487,7 +11498,7 @@
       </c>
       <c r="D92" s="37"/>
       <c r="E92" s="37" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="F92" s="37"/>
       <c r="G92" s="37">
@@ -11495,7 +11506,7 @@
       </c>
       <c r="H92" s="37"/>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="37">
         <v>1090160</v>
       </c>
@@ -11505,7 +11516,7 @@
       <c r="C93" s="37"/>
       <c r="D93" s="37"/>
       <c r="E93" s="37" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="F93" s="37"/>
       <c r="G93" s="37"/>
@@ -11513,7 +11524,7 @@
         <v>10902</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" s="37">
         <v>1100010</v>
       </c>
@@ -11523,7 +11534,7 @@
       <c r="C94" s="37"/>
       <c r="D94" s="37"/>
       <c r="E94" s="37" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="F94" s="37"/>
       <c r="G94" s="37">
@@ -11531,7 +11542,7 @@
       </c>
       <c r="H94" s="37"/>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" s="37">
         <v>1100020</v>
       </c>
@@ -11539,11 +11550,11 @@
         <v>0</v>
       </c>
       <c r="C95" s="37" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D95" s="37"/>
       <c r="E95" s="37" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="F95" s="37"/>
       <c r="G95" s="37">
@@ -11551,7 +11562,7 @@
       </c>
       <c r="H95" s="37"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="37">
         <v>1100030</v>
       </c>
@@ -11561,7 +11572,7 @@
       <c r="C96" s="37"/>
       <c r="D96" s="37"/>
       <c r="E96" s="37" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="F96" s="37"/>
       <c r="G96" s="37">
@@ -11569,7 +11580,7 @@
       </c>
       <c r="H96" s="37"/>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" s="37">
         <v>1100040</v>
       </c>
@@ -11577,11 +11588,11 @@
         <v>0</v>
       </c>
       <c r="C97" s="37" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D97" s="37"/>
       <c r="E97" s="37" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="F97" s="37"/>
       <c r="G97" s="37">
@@ -11589,7 +11600,7 @@
       </c>
       <c r="H97" s="37"/>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" s="37">
         <v>1100050</v>
       </c>
@@ -11597,11 +11608,11 @@
         <v>0</v>
       </c>
       <c r="C98" s="37" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D98" s="37"/>
       <c r="E98" s="37" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="F98" s="37"/>
       <c r="G98" s="37">
@@ -11609,7 +11620,7 @@
       </c>
       <c r="H98" s="37"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" s="37">
         <v>1100060</v>
       </c>
@@ -11621,7 +11632,7 @@
       </c>
       <c r="D99" s="37"/>
       <c r="E99" s="37" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F99" s="37"/>
       <c r="G99" s="37">
@@ -11629,7 +11640,7 @@
       </c>
       <c r="H99" s="37"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" s="37">
         <v>1100070</v>
       </c>
@@ -11637,11 +11648,11 @@
         <v>0</v>
       </c>
       <c r="C100" s="37" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D100" s="37"/>
       <c r="E100" s="37" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="F100" s="37"/>
       <c r="G100" s="37">
@@ -11649,7 +11660,7 @@
       </c>
       <c r="H100" s="37"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" s="37">
         <v>1100080</v>
       </c>
@@ -11661,7 +11672,7 @@
       </c>
       <c r="D101" s="37"/>
       <c r="E101" s="37" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="F101" s="37"/>
       <c r="G101" s="37">
@@ -11669,7 +11680,7 @@
       </c>
       <c r="H101" s="37"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" s="37">
         <v>1100090</v>
       </c>
@@ -11679,7 +11690,7 @@
       <c r="C102" s="37"/>
       <c r="D102" s="37"/>
       <c r="E102" s="37" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="F102" s="37"/>
       <c r="G102" s="37"/>
@@ -11687,7 +11698,7 @@
         <v>11001</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" s="37">
         <v>1100100</v>
       </c>
@@ -11697,7 +11708,7 @@
       <c r="C103" s="37"/>
       <c r="D103" s="37"/>
       <c r="E103" s="37" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F103" s="37"/>
       <c r="G103" s="37">
@@ -11705,7 +11716,7 @@
       </c>
       <c r="H103" s="37"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" s="37">
         <v>1100110</v>
       </c>
@@ -11713,11 +11724,11 @@
         <v>0</v>
       </c>
       <c r="C104" s="37" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D104" s="37"/>
       <c r="E104" s="37" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="F104" s="37"/>
       <c r="G104" s="37">
@@ -11725,7 +11736,7 @@
       </c>
       <c r="H104" s="37"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" s="37">
         <v>1100120</v>
       </c>
@@ -11735,7 +11746,7 @@
       <c r="C105" s="37"/>
       <c r="D105" s="37"/>
       <c r="E105" s="37" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="F105" s="37"/>
       <c r="G105" s="37">
@@ -11743,7 +11754,7 @@
       </c>
       <c r="H105" s="37"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" s="37">
         <v>1100130</v>
       </c>
@@ -11753,7 +11764,7 @@
       <c r="C106" s="37"/>
       <c r="D106" s="37"/>
       <c r="E106" s="37" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="F106" s="37"/>
       <c r="G106" s="37">
@@ -11761,7 +11772,7 @@
       </c>
       <c r="H106" s="37"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" s="37">
         <v>1100140</v>
       </c>
@@ -11769,11 +11780,11 @@
         <v>0</v>
       </c>
       <c r="C107" s="37" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D107" s="37"/>
       <c r="E107" s="37" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="F107" s="37"/>
       <c r="G107" s="37">
@@ -11781,7 +11792,7 @@
       </c>
       <c r="H107" s="37"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" s="37">
         <v>1100150</v>
       </c>
@@ -11793,7 +11804,7 @@
       </c>
       <c r="D108" s="37"/>
       <c r="E108" s="37" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="F108" s="37"/>
       <c r="G108" s="37">
@@ -11801,7 +11812,7 @@
       </c>
       <c r="H108" s="37"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" s="37">
         <v>1100160</v>
       </c>
@@ -11809,11 +11820,11 @@
         <v>0</v>
       </c>
       <c r="C109" s="37" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D109" s="37"/>
       <c r="E109" s="37" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="F109" s="37"/>
       <c r="G109" s="37">
@@ -11821,7 +11832,7 @@
       </c>
       <c r="H109" s="37"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" s="37">
         <v>1100170</v>
       </c>
@@ -11831,7 +11842,7 @@
       <c r="C110" s="37"/>
       <c r="D110" s="37"/>
       <c r="E110" s="37" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="F110" s="37"/>
       <c r="G110" s="37">
@@ -11839,7 +11850,7 @@
       </c>
       <c r="H110" s="37"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" s="37">
         <v>1100180</v>
       </c>
@@ -11851,7 +11862,7 @@
       </c>
       <c r="D111" s="37"/>
       <c r="E111" s="37" t="s">
-        <v>557</v>
+        <v>552</v>
       </c>
       <c r="F111" s="37"/>
       <c r="G111" s="37">
@@ -11859,7 +11870,7 @@
       </c>
       <c r="H111" s="37"/>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" s="37">
         <v>1100190</v>
       </c>
@@ -11871,7 +11882,7 @@
       </c>
       <c r="D112" s="37"/>
       <c r="E112" s="37" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="F112" s="37"/>
       <c r="G112" s="37">
@@ -11879,7 +11890,7 @@
       </c>
       <c r="H112" s="37"/>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" s="37">
         <v>1100200</v>
       </c>
@@ -11889,7 +11900,7 @@
       <c r="C113" s="37"/>
       <c r="D113" s="37"/>
       <c r="E113" s="37" t="s">
-        <v>559</v>
+        <v>554</v>
       </c>
       <c r="F113" s="37"/>
       <c r="G113" s="37">
@@ -11897,7 +11908,7 @@
       </c>
       <c r="H113" s="37"/>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" s="37">
         <v>1100210</v>
       </c>
@@ -11905,11 +11916,11 @@
         <v>0</v>
       </c>
       <c r="C114" s="37" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="D114" s="37"/>
       <c r="E114" s="37" t="s">
-        <v>560</v>
+        <v>555</v>
       </c>
       <c r="F114" s="37"/>
       <c r="G114" s="37">
@@ -11917,7 +11928,7 @@
       </c>
       <c r="H114" s="37"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" s="37">
         <v>1100220</v>
       </c>
@@ -11927,7 +11938,7 @@
       <c r="C115" s="37"/>
       <c r="D115" s="37"/>
       <c r="E115" s="37" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
       <c r="F115" s="37"/>
       <c r="G115" s="37">
@@ -11935,7 +11946,7 @@
       </c>
       <c r="H115" s="37"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" s="37">
         <v>1100230</v>
       </c>
@@ -11945,7 +11956,7 @@
       <c r="C116" s="37"/>
       <c r="D116" s="37"/>
       <c r="E116" s="37" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="F116" s="37"/>
       <c r="G116" s="37"/>
@@ -11953,7 +11964,7 @@
         <v>11002</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" s="37"/>
       <c r="B117" s="37"/>
       <c r="C117" s="37"/>
@@ -11963,7 +11974,7 @@
       <c r="G117" s="37"/>
       <c r="H117" s="37"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" s="37"/>
       <c r="B118" s="37"/>
       <c r="C118" s="37"/>
@@ -11973,7 +11984,7 @@
       <c r="G118" s="37"/>
       <c r="H118" s="37"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" s="37"/>
       <c r="B119" s="37"/>
       <c r="C119" s="37"/>
@@ -11992,19 +12003,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:H24"/>
-  <sheetFormatPr defaultRowHeight="17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" style="28" customWidth="1"/>
+    <col min="2" max="2" width="15.625" style="28" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="33.25" customWidth="1"/>
-    <col min="5" max="5" width="77.33203125" customWidth="1"/>
-    <col min="6" max="6" width="14.08203125" customWidth="1"/>
+    <col min="5" max="5" width="77.375" customWidth="1"/>
+    <col min="6" max="6" width="14.125" customWidth="1"/>
     <col min="7" max="7" width="49.75" customWidth="1"/>
-    <col min="8" max="8" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="22.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="26.25" customHeight="1">
+    <row r="1" spans="1:8" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
@@ -12030,7 +12041,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="37">
         <v>10501</v>
       </c>
@@ -12040,19 +12051,19 @@
       <c r="C2" s="37"/>
       <c r="D2" s="37"/>
       <c r="E2" s="37" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="F2" s="37">
         <v>1050080</v>
       </c>
       <c r="G2" s="37" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="H2" s="37" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="37">
         <v>10501</v>
       </c>
@@ -12062,19 +12073,19 @@
       <c r="C3" s="37"/>
       <c r="D3" s="37"/>
       <c r="E3" s="37" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="F3" s="37">
         <v>1050110</v>
       </c>
       <c r="G3" s="37" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="H3" s="37" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" s="37">
         <v>10502</v>
       </c>
@@ -12086,13 +12097,13 @@
       <c r="E4" s="37"/>
       <c r="F4" s="37"/>
       <c r="G4" s="37" t="s">
-        <v>567</v>
+        <v>562</v>
       </c>
       <c r="H4" s="37" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="37">
         <v>10601</v>
       </c>
@@ -12102,19 +12113,19 @@
       <c r="C5" s="37"/>
       <c r="D5" s="37"/>
       <c r="E5" s="37" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="F5" s="37">
         <v>1060100</v>
       </c>
       <c r="G5" s="37" t="s">
-        <v>569</v>
+        <v>564</v>
       </c>
       <c r="H5" s="37" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="37">
         <v>10601</v>
       </c>
@@ -12124,43 +12135,43 @@
       <c r="C6" s="37"/>
       <c r="D6" s="37"/>
       <c r="E6" s="37" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
       <c r="F6" s="37">
         <v>1060140</v>
       </c>
       <c r="G6" s="37" t="s">
-        <v>571</v>
+        <v>566</v>
       </c>
       <c r="H6" s="37" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>10601</v>
       </c>
       <c r="B7" s="38" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C7" s="37" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D7" s="37" t="s">
-        <v>573</v>
+        <v>568</v>
       </c>
       <c r="E7" s="37" t="s">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="F7" s="37">
         <v>1060170</v>
       </c>
       <c r="G7" s="37"/>
       <c r="H7" s="37" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" s="37">
         <v>10602</v>
       </c>
@@ -12172,13 +12183,13 @@
       <c r="E8" s="37"/>
       <c r="F8" s="37"/>
       <c r="G8" s="37" t="s">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="H8" s="37" t="s">
-        <v>577</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="37">
         <v>10701</v>
       </c>
@@ -12188,65 +12199,65 @@
       <c r="C9" s="37"/>
       <c r="D9" s="37"/>
       <c r="E9" s="37" t="s">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="F9" s="37">
         <v>1070100</v>
       </c>
       <c r="G9" s="37" t="s">
-        <v>578</v>
+        <v>573</v>
       </c>
       <c r="H9" s="37" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="34">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>10701</v>
       </c>
       <c r="B10" s="38" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C10" s="37" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="D10" s="37" t="s">
-        <v>580</v>
+        <v>575</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F10" s="37">
         <v>1070140</v>
       </c>
       <c r="G10" s="37"/>
       <c r="H10" s="37" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" ht="34">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A11" s="37">
         <v>10702</v>
       </c>
       <c r="B11" s="38" t="s">
+        <v>412</v>
+      </c>
+      <c r="C11" s="37" t="s">
         <v>413</v>
       </c>
-      <c r="C11" s="37" t="s">
-        <v>414</v>
-      </c>
       <c r="D11" s="37" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="E11" s="37"/>
       <c r="F11" s="37"/>
       <c r="G11" s="40" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="H11" s="37" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" ht="51">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A12" s="37">
         <v>10702</v>
       </c>
@@ -12258,13 +12269,13 @@
       <c r="E12" s="37"/>
       <c r="F12" s="37"/>
       <c r="G12" s="40" t="s">
-        <v>602</v>
+        <v>597</v>
       </c>
       <c r="H12" s="37" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>10801</v>
       </c>
@@ -12274,17 +12285,17 @@
       <c r="C13" s="37"/>
       <c r="D13" s="37"/>
       <c r="E13" s="37" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="F13" s="37">
         <v>1080080</v>
       </c>
       <c r="G13" s="37"/>
       <c r="H13" s="37" t="s">
-        <v>585</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="37">
         <v>10801</v>
       </c>
@@ -12294,17 +12305,17 @@
       <c r="C14" s="37"/>
       <c r="D14" s="37"/>
       <c r="E14" s="37" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="F14" s="37">
         <v>1080110</v>
       </c>
       <c r="G14" s="37"/>
       <c r="H14" s="37" t="s">
-        <v>586</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="37">
         <v>10801</v>
       </c>
@@ -12314,17 +12325,17 @@
       <c r="C15" s="37"/>
       <c r="D15" s="37"/>
       <c r="E15" s="37" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="F15" s="37">
         <v>1080140</v>
       </c>
       <c r="G15" s="37"/>
       <c r="H15" s="37" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="37">
         <v>10802</v>
       </c>
@@ -12336,13 +12347,13 @@
       <c r="E16" s="37"/>
       <c r="F16" s="37"/>
       <c r="G16" s="37" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="H16" s="37" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="37">
         <v>10901</v>
       </c>
@@ -12352,17 +12363,17 @@
       <c r="C17" s="37"/>
       <c r="D17" s="37"/>
       <c r="E17" s="37" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="F17" s="37">
         <v>1090100</v>
       </c>
       <c r="G17" s="37"/>
       <c r="H17" s="37" t="s">
-        <v>590</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="37">
         <v>10901</v>
       </c>
@@ -12372,17 +12383,17 @@
       <c r="C18" s="37"/>
       <c r="D18" s="37"/>
       <c r="E18" s="37" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="F18" s="37">
         <v>1090120</v>
       </c>
       <c r="G18" s="37"/>
       <c r="H18" s="37" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>10902</v>
       </c>
@@ -12394,13 +12405,13 @@
       <c r="E19" s="37"/>
       <c r="F19" s="37"/>
       <c r="G19" s="37" t="s">
-        <v>592</v>
+        <v>587</v>
       </c>
       <c r="H19" s="37" t="s">
-        <v>593</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="37">
         <v>11001</v>
       </c>
@@ -12410,19 +12421,19 @@
       <c r="C20" s="37"/>
       <c r="D20" s="37"/>
       <c r="E20" s="37" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="F20" s="37">
         <v>1100100</v>
       </c>
       <c r="G20" s="37" t="s">
-        <v>594</v>
+        <v>589</v>
       </c>
       <c r="H20" s="37" t="s">
-        <v>595</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="37">
         <v>11001</v>
       </c>
@@ -12432,63 +12443,63 @@
       <c r="C21" s="37"/>
       <c r="D21" s="37"/>
       <c r="E21" s="37" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="F21" s="37">
         <v>1100130</v>
       </c>
       <c r="G21" s="37"/>
       <c r="H21" s="37" t="s">
-        <v>596</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>11001</v>
       </c>
       <c r="B22" s="38" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="C22" s="37" t="s">
-        <v>597</v>
+        <v>592</v>
       </c>
       <c r="D22" s="37" t="s">
-        <v>598</v>
+        <v>593</v>
       </c>
       <c r="E22" s="37" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="F22" s="37">
         <v>1100170</v>
       </c>
       <c r="G22" s="37"/>
       <c r="H22" s="37" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" ht="34">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="33" x14ac:dyDescent="0.3">
       <c r="A23" s="37">
         <v>11002</v>
       </c>
       <c r="B23" s="37" t="s">
+        <v>412</v>
+      </c>
+      <c r="C23" s="37" t="s">
         <v>413</v>
       </c>
-      <c r="C23" s="37" t="s">
-        <v>414</v>
-      </c>
       <c r="D23" s="37" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="E23" s="37"/>
       <c r="F23" s="37"/>
       <c r="G23" s="40" t="s">
-        <v>603</v>
+        <v>598</v>
       </c>
       <c r="H23" s="37" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="51">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A24" s="37">
         <v>11002</v>
       </c>
@@ -12500,15 +12511,14 @@
       <c r="E24" s="37"/>
       <c r="F24" s="37"/>
       <c r="G24" s="40" t="s">
-        <v>604</v>
+        <v>599</v>
       </c>
       <c r="H24" s="37" t="s">
-        <v>600</v>
+        <v>595</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="14" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>